--- a/data/out/test1/001328648_Python版_1pt.xlsx
+++ b/data/out/test1/001328648_Python版_1pt.xlsx
@@ -19,13 +19,37 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="13.14"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="10.9"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="9.800000000000001"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="6.5"/>
     </font>
     <font>
       <name val="MS Gothic"/>
@@ -40,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -120,11 +144,29 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,31 +179,112 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -653,7 +776,7 @@
     </row>
     <row r="5">
       <c r="B5" s="7"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>※太枠の中に書いてください。</t>
         </is>
@@ -662,27 +785,27 @@
     </row>
     <row r="6">
       <c r="B6" s="7"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>（地方）法務局</t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>支局・出張所</t>
         </is>
       </c>
-      <c r="AK6" s="8" t="inlineStr">
+      <c r="AK6" s="11" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="AO6" s="8" t="inlineStr">
+      <c r="AO6" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AT6" s="8" t="inlineStr">
+      <c r="AT6" s="11" t="inlineStr">
         <is>
           <t>日届出</t>
         </is>
@@ -694,7 +817,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
@@ -708,13 +831,13 @@
       <c r="M7" s="5"/>
       <c r="N7" s="6"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="1"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -754,22 +877,24 @@
     </row>
     <row r="8">
       <c r="B8" s="7"/>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
       <c r="N8" s="9"/>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
       </c>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="7"/>
       <c r="W8" s="4"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
@@ -805,88 +930,88 @@
     </row>
     <row r="9">
       <c r="B9" s="7"/>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー廃止届出</t>
         </is>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="14"/>
-      <c r="AG9" s="14"/>
-      <c r="AH9" s="14"/>
-      <c r="AI9" s="14"/>
-      <c r="AJ9" s="14"/>
-      <c r="AK9" s="14"/>
-      <c r="AL9" s="14"/>
-      <c r="AM9" s="14"/>
-      <c r="AN9" s="14"/>
-      <c r="AO9" s="14"/>
-      <c r="AP9" s="14"/>
-      <c r="AQ9" s="14"/>
-      <c r="AR9" s="14"/>
-      <c r="AS9" s="14"/>
-      <c r="AT9" s="14"/>
-      <c r="AU9" s="14"/>
-      <c r="AV9" s="14"/>
-      <c r="AW9" s="14"/>
-      <c r="AX9" s="14"/>
-      <c r="AY9" s="14"/>
-      <c r="AZ9" s="14"/>
-      <c r="BA9" s="15"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AI9" s="19"/>
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+      <c r="AP9" s="19"/>
+      <c r="AQ9" s="19"/>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="19"/>
+      <c r="AT9" s="19"/>
+      <c r="AU9" s="19"/>
+      <c r="AV9" s="19"/>
+      <c r="AW9" s="19"/>
+      <c r="AX9" s="19"/>
+      <c r="AY9" s="19"/>
+      <c r="AZ9" s="19"/>
+      <c r="BA9" s="20"/>
       <c r="BC9" s="9"/>
     </row>
     <row r="10">
       <c r="B10" s="7"/>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>廃止届出</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
       <c r="N10" s="9"/>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
       <c r="P10" s="3"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="2"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="17" t="inlineStr">
+      <c r="W10" s="23" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
@@ -925,89 +1050,91 @@
     </row>
     <row r="11">
       <c r="B11" s="7"/>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印をつけてください。)</t>
         </is>
       </c>
       <c r="N11" s="9"/>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="25" t="inlineStr">
         <is>
           <t>印資格(</t>
         </is>
       </c>
       <c r="P11" s="6"/>
-      <c r="W11" s="18" t="inlineStr">
+      <c r="Q11" s="9"/>
+      <c r="R11" s="7"/>
+      <c r="W11" s="26" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
       </c>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
-      <c r="AI11" s="14"/>
-      <c r="AJ11" s="14"/>
-      <c r="AK11" s="14"/>
-      <c r="AL11" s="14"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-      <c r="AO11" s="14"/>
-      <c r="AP11" s="14"/>
-      <c r="AQ11" s="14"/>
-      <c r="AR11" s="14"/>
-      <c r="AS11" s="14"/>
-      <c r="AT11" s="14"/>
-      <c r="AU11" s="14"/>
-      <c r="AV11" s="14"/>
-      <c r="AW11" s="14"/>
-      <c r="AX11" s="14"/>
-      <c r="AY11" s="14"/>
-      <c r="AZ11" s="19" t="inlineStr">
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="19"/>
+      <c r="AT11" s="19"/>
+      <c r="AU11" s="19"/>
+      <c r="AV11" s="19"/>
+      <c r="AW11" s="19"/>
+      <c r="AX11" s="19"/>
+      <c r="AY11" s="19"/>
+      <c r="AZ11" s="27" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="BA11" s="15"/>
+      <c r="BA11" s="20"/>
       <c r="BC11" s="9"/>
     </row>
     <row r="12">
       <c r="B12" s="7"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
       <c r="N12" s="9"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t>鑑氏名</t>
         </is>
       </c>
       <c r="P12" s="9"/>
-      <c r="Q12" s="16" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t>資 格</t>
         </is>
       </c>
-      <c r="R12" s="2"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="17" t="inlineStr">
+      <c r="W12" s="30" t="inlineStr">
         <is>
           <t>( )</t>
         </is>
@@ -1046,86 +1173,87 @@
     </row>
     <row r="13">
       <c r="B13" s="7"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印を</t>
         </is>
       </c>
       <c r="N13" s="9"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O13" s="28" t="inlineStr">
         <is>
           <t>提</t>
         </is>
       </c>
       <c r="P13" s="9"/>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="31" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
       </c>
-      <c r="W13" s="13"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="14"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
-      <c r="AP13" s="14"/>
-      <c r="AQ13" s="14"/>
-      <c r="AR13" s="14"/>
-      <c r="AS13" s="14"/>
-      <c r="AT13" s="14"/>
-      <c r="AU13" s="14"/>
-      <c r="AV13" s="14"/>
-      <c r="AW13" s="14"/>
-      <c r="AX13" s="14"/>
-      <c r="AY13" s="14"/>
-      <c r="AZ13" s="14"/>
-      <c r="BA13" s="15"/>
+      <c r="R13" s="7"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="20"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="20"/>
+      <c r="AS13" s="18"/>
+      <c r="AT13" s="19"/>
+      <c r="AU13" s="19"/>
+      <c r="AV13" s="19"/>
+      <c r="AW13" s="19"/>
+      <c r="AX13" s="20"/>
+      <c r="AY13" s="18"/>
+      <c r="AZ13" s="19"/>
+      <c r="BA13" s="20"/>
       <c r="BC13" s="9"/>
     </row>
     <row r="14">
       <c r="B14" s="7"/>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>つけてください。)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="18" t="inlineStr">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="5"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="4"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -1133,21 +1261,21 @@
       <c r="W14" s="4"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="4"/>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="4"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="5"/>
-      <c r="AM14" s="5"/>
-      <c r="AN14" s="10" t="inlineStr">
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="4"/>
+      <c r="AN14" s="35" t="inlineStr">
         <is>
           <t>年</t>
         </is>
@@ -1155,35 +1283,35 @@
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
       <c r="AQ14" s="5"/>
-      <c r="AR14" s="10" t="inlineStr">
+      <c r="AR14" s="36" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AS14" s="5"/>
+      <c r="AS14" s="4"/>
       <c r="AT14" s="5"/>
       <c r="AU14" s="5"/>
       <c r="AV14" s="5"/>
-      <c r="AW14" s="10" t="inlineStr">
+      <c r="AW14" s="35" t="inlineStr">
         <is>
           <t>日生</t>
         </is>
       </c>
-      <c r="AX14" s="5"/>
-      <c r="AY14" s="5"/>
+      <c r="AX14" s="6"/>
+      <c r="AY14" s="4"/>
       <c r="AZ14" s="5"/>
       <c r="BA14" s="6"/>
       <c r="BC14" s="9"/>
     </row>
     <row r="15">
       <c r="B15" s="7"/>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>登記所に提出した</t>
         </is>
@@ -1197,81 +1325,81 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="16" t="inlineStr">
+      <c r="O15" s="21" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
       <c r="P15" s="3"/>
-      <c r="Q15" s="18" t="inlineStr">
+      <c r="Q15" s="38" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="18" t="inlineStr">
+      <c r="R15" s="18"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="26" t="inlineStr">
         <is>
           <t>大・昭・平・西暦 年 月 日生</t>
         </is>
       </c>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-      <c r="AF15" s="14"/>
-      <c r="AG15" s="14"/>
-      <c r="AH15" s="14"/>
-      <c r="AI15" s="14"/>
-      <c r="AJ15" s="14"/>
-      <c r="AK15" s="14"/>
-      <c r="AL15" s="14"/>
-      <c r="AM15" s="14"/>
-      <c r="AN15" s="14"/>
-      <c r="AO15" s="14"/>
-      <c r="AP15" s="14"/>
-      <c r="AQ15" s="14"/>
-      <c r="AR15" s="14"/>
-      <c r="AS15" s="14"/>
-      <c r="AT15" s="14"/>
-      <c r="AU15" s="14"/>
-      <c r="AV15" s="14"/>
-      <c r="AW15" s="14"/>
-      <c r="AX15" s="14"/>
-      <c r="AY15" s="14"/>
-      <c r="AZ15" s="14"/>
-      <c r="BA15" s="15"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="18"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="20"/>
+      <c r="AM15" s="18"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19"/>
+      <c r="AP15" s="19"/>
+      <c r="AQ15" s="19"/>
+      <c r="AR15" s="20"/>
+      <c r="AS15" s="18"/>
+      <c r="AT15" s="19"/>
+      <c r="AU15" s="19"/>
+      <c r="AV15" s="19"/>
+      <c r="AW15" s="19"/>
+      <c r="AX15" s="20"/>
+      <c r="AY15" s="18"/>
+      <c r="AZ15" s="19"/>
+      <c r="BA15" s="20"/>
       <c r="BC15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="7"/>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>登 記 所 に 提 出 し た</t>
         </is>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="D16" s="19"/>
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>印鑑の押印欄印鑑カード番号</t>
         </is>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="15"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="20"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
@@ -1315,7 +1443,7 @@
     </row>
     <row r="17">
       <c r="B17" s="7"/>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>印 鑑 の 押 印 欄</t>
         </is>
@@ -1331,75 +1459,75 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="18" t="inlineStr">
+      <c r="O17" s="26" t="inlineStr">
         <is>
           <t>印鑑カード番号</t>
         </is>
       </c>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="19" t="inlineStr">
+      <c r="P17" s="19"/>
+      <c r="Q17" s="40" t="inlineStr">
         <is>
           <t>カード廃止の理由</t>
         </is>
       </c>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="19" t="inlineStr">
+      <c r="R17" s="18"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
+      <c r="AC17" s="19"/>
+      <c r="AD17" s="19"/>
+      <c r="AE17" s="32" t="inlineStr">
         <is>
           <t>亡失（なくなった）</t>
         </is>
       </c>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="14"/>
-      <c r="AH17" s="14"/>
-      <c r="AI17" s="14"/>
-      <c r="AJ17" s="14"/>
-      <c r="AK17" s="14"/>
-      <c r="AL17" s="14"/>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="14"/>
-      <c r="AO17" s="14"/>
-      <c r="AP17" s="14"/>
-      <c r="AQ17" s="14"/>
-      <c r="AR17" s="19" t="inlineStr">
+      <c r="AF17" s="19"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19"/>
+      <c r="AJ17" s="19"/>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="19"/>
+      <c r="AP17" s="19"/>
+      <c r="AQ17" s="19"/>
+      <c r="AR17" s="32" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AS17" s="14"/>
-      <c r="AT17" s="14"/>
-      <c r="AU17" s="14"/>
-      <c r="AV17" s="14"/>
-      <c r="AW17" s="14"/>
-      <c r="AX17" s="14"/>
-      <c r="AY17" s="14"/>
-      <c r="AZ17" s="14"/>
-      <c r="BA17" s="15"/>
+      <c r="AS17" s="19"/>
+      <c r="AT17" s="19"/>
+      <c r="AU17" s="19"/>
+      <c r="AV17" s="19"/>
+      <c r="AW17" s="19"/>
+      <c r="AX17" s="19"/>
+      <c r="AY17" s="19"/>
+      <c r="AZ17" s="19"/>
+      <c r="BA17" s="20"/>
       <c r="BC17" s="9"/>
     </row>
     <row r="18">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="O18" s="41" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、</t>
         </is>
       </c>
       <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="4"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -1412,7 +1540,7 @@
       <c r="AB18" s="5"/>
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
-      <c r="AE18" s="10" t="inlineStr">
+      <c r="AE18" s="12" t="inlineStr">
         <is>
           <t>汚損（著しく汚れた)</t>
         </is>
@@ -1445,17 +1573,17 @@
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O19" s="14" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、 汚損（著しく汚れた)</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="Q19" s="42" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="inlineStr">
+      <c r="AE19" s="10" t="inlineStr">
         <is>
           <t>き損（破損した）</t>
         </is>
@@ -1467,79 +1595,80 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="18" t="inlineStr">
+      <c r="O20" s="26" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。 き損（破損した）</t>
         </is>
       </c>
-      <c r="P20" s="19" t="inlineStr">
+      <c r="P20" s="27" t="inlineStr">
         <is>
           <t>申請人（注２）</t>
         </is>
       </c>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="19" t="inlineStr">
+      <c r="Q20" s="20"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="27" t="inlineStr">
         <is>
           <t>印鑑提出者本人代理人</t>
         </is>
       </c>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="14"/>
-      <c r="AG20" s="14"/>
-      <c r="AH20" s="14"/>
-      <c r="AI20" s="14"/>
-      <c r="AJ20" s="14"/>
-      <c r="AK20" s="14"/>
-      <c r="AL20" s="14"/>
-      <c r="AM20" s="14"/>
-      <c r="AN20" s="14"/>
-      <c r="AO20" s="14"/>
-      <c r="AP20" s="14"/>
-      <c r="AQ20" s="14"/>
-      <c r="AR20" s="14"/>
-      <c r="AS20" s="14"/>
-      <c r="AT20" s="14"/>
-      <c r="AU20" s="14"/>
-      <c r="AV20" s="14"/>
-      <c r="AW20" s="14"/>
-      <c r="AX20" s="14"/>
-      <c r="AY20" s="14"/>
-      <c r="AZ20" s="14"/>
-      <c r="BA20" s="15"/>
-      <c r="BC20" s="9"/>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="19"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="19"/>
+      <c r="AI20" s="19"/>
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="19"/>
+      <c r="AO20" s="19"/>
+      <c r="AP20" s="19"/>
+      <c r="AQ20" s="19"/>
+      <c r="AR20" s="19"/>
+      <c r="AS20" s="19"/>
+      <c r="AT20" s="19"/>
+      <c r="AU20" s="19"/>
+      <c r="AV20" s="19"/>
+      <c r="AW20" s="19"/>
+      <c r="AX20" s="19"/>
+      <c r="AY20" s="19"/>
+      <c r="AZ20" s="19"/>
+      <c r="BA20" s="20"/>
+      <c r="BB20" s="19"/>
+      <c r="BC20" s="20"/>
     </row>
     <row r="21">
       <c r="B21" s="7"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="16" t="inlineStr">
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="21" t="inlineStr">
         <is>
           <t>申 請 人（注２） 印鑑提出者本人 代理人</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="13" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
@@ -1581,12 +1710,13 @@
       <c r="AY21" s="2"/>
       <c r="AZ21" s="2"/>
       <c r="BA21" s="3"/>
-      <c r="BC21" s="9"/>
+      <c r="BB21" s="5"/>
+      <c r="BC21" s="6"/>
     </row>
     <row r="22">
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>（印鑑は鮮明に押</t>
         </is>
@@ -1601,41 +1731,44 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="15" t="inlineStr">
         <is>
           <t>住 所</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="Q22" s="43" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
+      <c r="R22" s="7"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="7"/>
       <c r="BC22" s="9"/>
     </row>
     <row r="23">
       <c r="B23" s="7"/>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>（ 印 鑑 は 鮮 明 に 押</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="39" t="inlineStr">
         <is>
           <t>印してください。）氏名</t>
         </is>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="16" t="inlineStr">
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="21" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
@@ -1682,7 +1815,7 @@
     </row>
     <row r="24">
       <c r="B24" s="7"/>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>印 し て く だ さ い 。 ）</t>
         </is>
@@ -1698,7 +1831,7 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
-      <c r="O24" s="10" t="inlineStr">
+      <c r="O24" s="44" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
@@ -1745,22 +1878,22 @@
     </row>
     <row r="25">
       <c r="B25" s="7"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>委 任 状</t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="X25" s="10" t="inlineStr">
         <is>
           <t>委</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
+      <c r="AD25" s="10" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="10" t="inlineStr">
         <is>
           <t>状</t>
         </is>
@@ -1770,13 +1903,13 @@
     </row>
     <row r="26">
       <c r="B26" s="7"/>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="45" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
@@ -1792,17 +1925,17 @@
     </row>
     <row r="27">
       <c r="B27" s="7"/>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J27" s="46" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
@@ -1816,17 +1949,17 @@
     </row>
     <row r="28">
       <c r="B28" s="7"/>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>を代理人と定め、 印鑑の廃止届出、 印鑑カードの廃止届出、 印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>を代理人と定め、の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
@@ -1836,22 +1969,22 @@
     </row>
     <row r="29">
       <c r="B29" s="7"/>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>の廃止届出、 添付書面の原本還付請求及び受領の権限を委任します。</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="U29" s="10" t="inlineStr">
         <is>
           <t>日</t>
         </is>
@@ -1861,12 +1994,12 @@
     </row>
     <row r="30">
       <c r="B30" s="7"/>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>年 月 日</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
@@ -1876,57 +2009,69 @@
     </row>
     <row r="31">
       <c r="B31" s="7"/>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>住 所</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="AR31" s="8" t="inlineStr">
+      <c r="W31" s="9"/>
+      <c r="X31" s="7"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="7"/>
+      <c r="AR31" s="24" t="inlineStr">
         <is>
           <t>登記所に提</t>
         </is>
       </c>
+      <c r="AY31" s="9"/>
+      <c r="AZ31" s="7"/>
       <c r="BA31" s="9"/>
       <c r="BC31" s="9"/>
     </row>
     <row r="32">
       <c r="B32" s="7"/>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>登 記 所 に 提</t>
         </is>
       </c>
-      <c r="AN32" s="8" t="inlineStr">
+      <c r="W32" s="9"/>
+      <c r="X32" s="7"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="7"/>
+      <c r="AN32" s="10" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AR32" s="8" t="inlineStr">
+      <c r="AR32" s="24" t="inlineStr">
         <is>
           <t>出した印鑑</t>
         </is>
       </c>
+      <c r="AY32" s="9"/>
+      <c r="AZ32" s="7"/>
       <c r="BA32" s="9"/>
       <c r="BC32" s="9"/>
     </row>
     <row r="33">
       <c r="B33" s="7"/>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>（注１）登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
@@ -1936,12 +2081,12 @@
     </row>
     <row r="34">
       <c r="B34" s="7"/>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
@@ -1951,12 +2096,12 @@
     </row>
     <row r="35">
       <c r="B35" s="7"/>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>出 し た 印 鑑</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）は、□にレ印をつけてください。</t>
         </is>
@@ -1966,12 +2111,12 @@
     </row>
     <row r="36">
       <c r="B36" s="7"/>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>（注２）事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
@@ -1981,12 +2126,12 @@
     </row>
     <row r="37">
       <c r="B37" s="7"/>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>（注１） 登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="24" t="inlineStr">
         <is>
           <t>この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
         </is>
@@ -1996,17 +2141,17 @@
     </row>
     <row r="38">
       <c r="B38" s="7"/>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>（注３）村長の証明した印鑑証明書を添付してください。印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
       </c>
-      <c r="Z38" s="20"/>
+      <c r="Z38" s="22"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
@@ -2038,18 +2183,18 @@
     </row>
     <row r="39">
       <c r="B39" s="7"/>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="24" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合</t>
         </is>
       </c>
       <c r="Z39" s="4"/>
-      <c r="AA39" s="10" t="inlineStr">
+      <c r="AA39" s="44" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
@@ -2062,7 +2207,7 @@
       <c r="AG39" s="5"/>
       <c r="AH39" s="5"/>
       <c r="AI39" s="6"/>
-      <c r="AJ39" s="17" t="inlineStr">
+      <c r="AJ39" s="30" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
@@ -2070,7 +2215,7 @@
       <c r="AK39" s="5"/>
       <c r="AL39" s="5"/>
       <c r="AM39" s="6"/>
-      <c r="AN39" s="17" t="inlineStr">
+      <c r="AN39" s="30" t="inlineStr">
         <is>
           <t>調 査</t>
         </is>
@@ -2079,7 +2224,7 @@
       <c r="AP39" s="5"/>
       <c r="AQ39" s="5"/>
       <c r="AR39" s="6"/>
-      <c r="AS39" s="17" t="inlineStr">
+      <c r="AS39" s="30" t="inlineStr">
         <is>
           <t>入 力</t>
         </is>
@@ -2087,7 +2232,7 @@
       <c r="AT39" s="5"/>
       <c r="AU39" s="5"/>
       <c r="AV39" s="6"/>
-      <c r="AW39" s="17" t="inlineStr">
+      <c r="AW39" s="30" t="inlineStr">
         <is>
           <t>校 合</t>
         </is>
@@ -2100,75 +2245,76 @@
     </row>
     <row r="40">
       <c r="B40" s="7"/>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>は、□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="47" t="inlineStr">
         <is>
           <t>には、(注１)の押印及び(注２)の委任状は不要です。</t>
         </is>
       </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="14"/>
-      <c r="Z40" s="13"/>
-      <c r="AA40" s="14"/>
-      <c r="AB40" s="14"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="14"/>
-      <c r="AE40" s="14"/>
-      <c r="AF40" s="14"/>
-      <c r="AG40" s="14"/>
-      <c r="AH40" s="14"/>
-      <c r="AI40" s="15"/>
-      <c r="AJ40" s="13"/>
-      <c r="AK40" s="14"/>
-      <c r="AL40" s="14"/>
-      <c r="AM40" s="15"/>
-      <c r="AN40" s="13"/>
-      <c r="AO40" s="14"/>
-      <c r="AP40" s="14"/>
-      <c r="AQ40" s="14"/>
-      <c r="AR40" s="15"/>
-      <c r="AS40" s="13"/>
-      <c r="AT40" s="14"/>
-      <c r="AU40" s="14"/>
-      <c r="AV40" s="15"/>
-      <c r="AW40" s="13"/>
-      <c r="AX40" s="14"/>
-      <c r="AY40" s="14"/>
-      <c r="AZ40" s="14"/>
-      <c r="BA40" s="15"/>
-      <c r="BC40" s="9"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="19"/>
+      <c r="AC40" s="19"/>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="19"/>
+      <c r="AF40" s="19"/>
+      <c r="AG40" s="19"/>
+      <c r="AH40" s="19"/>
+      <c r="AI40" s="20"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="19"/>
+      <c r="AM40" s="20"/>
+      <c r="AN40" s="18"/>
+      <c r="AO40" s="19"/>
+      <c r="AP40" s="19"/>
+      <c r="AQ40" s="19"/>
+      <c r="AR40" s="20"/>
+      <c r="AS40" s="18"/>
+      <c r="AT40" s="20"/>
+      <c r="AU40" s="18"/>
+      <c r="AV40" s="20"/>
+      <c r="AW40" s="18"/>
+      <c r="AX40" s="20"/>
+      <c r="AY40" s="18"/>
+      <c r="AZ40" s="20"/>
+      <c r="BA40" s="17"/>
+      <c r="BB40" s="9"/>
+      <c r="BC40" s="48"/>
     </row>
     <row r="41">
-      <c r="B41" s="13"/>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="B41" s="18"/>
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>（注２） 代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="49" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>
@@ -2178,55 +2324,55 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="14"/>
-      <c r="AE41" s="14"/>
-      <c r="AF41" s="14"/>
-      <c r="AG41" s="14"/>
-      <c r="AH41" s="14"/>
-      <c r="AI41" s="14"/>
-      <c r="AJ41" s="14"/>
-      <c r="AK41" s="14"/>
-      <c r="AL41" s="14"/>
-      <c r="AM41" s="14"/>
-      <c r="AN41" s="14"/>
-      <c r="AO41" s="14"/>
-      <c r="AP41" s="14"/>
-      <c r="AQ41" s="14"/>
-      <c r="AR41" s="14"/>
-      <c r="AS41" s="14"/>
-      <c r="AT41" s="14"/>
-      <c r="AU41" s="14"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="14"/>
-      <c r="AX41" s="14"/>
-      <c r="AY41" s="14"/>
-      <c r="AZ41" s="14"/>
-      <c r="BA41" s="14"/>
-      <c r="BB41" s="14"/>
-      <c r="BC41" s="15"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="19"/>
+      <c r="AB41" s="19"/>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="19"/>
+      <c r="AE41" s="19"/>
+      <c r="AF41" s="19"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="19"/>
+      <c r="AI41" s="19"/>
+      <c r="AJ41" s="19"/>
+      <c r="AK41" s="19"/>
+      <c r="AL41" s="19"/>
+      <c r="AM41" s="19"/>
+      <c r="AN41" s="19"/>
+      <c r="AO41" s="19"/>
+      <c r="AP41" s="19"/>
+      <c r="AQ41" s="19"/>
+      <c r="AR41" s="20"/>
+      <c r="AS41" s="18"/>
+      <c r="AT41" s="20"/>
+      <c r="AU41" s="18"/>
+      <c r="AV41" s="20"/>
+      <c r="AW41" s="18"/>
+      <c r="AX41" s="20"/>
+      <c r="AY41" s="18"/>
+      <c r="AZ41" s="20"/>
+      <c r="BA41" s="18"/>
+      <c r="BB41" s="20"/>
+      <c r="BC41" s="17"/>
     </row>
     <row r="42">
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>

--- a/data/out/test1/001328648_Python版_1pt.xlsx
+++ b/data/out/test1/001328648_Python版_1pt.xlsx
@@ -64,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -144,29 +144,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,88 +182,70 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -836,8 +800,8 @@
           <t>商号・名称</t>
         </is>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="1"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -893,8 +857,6 @@
           <t>商号・名称</t>
         </is>
       </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="7"/>
       <c r="W8" s="4"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
@@ -947,43 +909,43 @@
           <t>本店・主たる事務所</t>
         </is>
       </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="1"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="3"/>
       <c r="W9" s="17"/>
       <c r="X9" s="18"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="18"/>
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="18"/>
+      <c r="AG9" s="18"/>
+      <c r="AH9" s="18"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="18"/>
+      <c r="AN9" s="18"/>
+      <c r="AO9" s="18"/>
+      <c r="AP9" s="18"/>
+      <c r="AQ9" s="18"/>
+      <c r="AR9" s="18"/>
+      <c r="AS9" s="18"/>
+      <c r="AT9" s="18"/>
+      <c r="AU9" s="18"/>
+      <c r="AV9" s="18"/>
+      <c r="AW9" s="18"/>
+      <c r="AX9" s="18"/>
+      <c r="AY9" s="18"/>
+      <c r="AZ9" s="18"/>
+      <c r="BA9" s="19"/>
       <c r="BC9" s="9"/>
     </row>
     <row r="10">
@@ -999,19 +961,19 @@
         </is>
       </c>
       <c r="N10" s="9"/>
-      <c r="O10" s="21" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
       <c r="P10" s="3"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="23" t="inlineStr">
+      <c r="W10" s="21" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
@@ -1055,59 +1017,57 @@
           <t>印鑑及び印鑑カー</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印をつけてください。)</t>
         </is>
       </c>
       <c r="N11" s="9"/>
-      <c r="O11" s="25" t="inlineStr">
+      <c r="O11" s="23" t="inlineStr">
         <is>
           <t>印資格(</t>
         </is>
       </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="7"/>
-      <c r="W11" s="26" t="inlineStr">
+      <c r="W11" s="24" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
       </c>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
-      <c r="AP11" s="19"/>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="19"/>
-      <c r="AS11" s="19"/>
-      <c r="AT11" s="19"/>
-      <c r="AU11" s="19"/>
-      <c r="AV11" s="19"/>
-      <c r="AW11" s="19"/>
-      <c r="AX11" s="19"/>
-      <c r="AY11" s="19"/>
-      <c r="AZ11" s="27" t="inlineStr">
+      <c r="X11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="18"/>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="18"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="18"/>
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="18"/>
+      <c r="AN11" s="18"/>
+      <c r="AO11" s="18"/>
+      <c r="AP11" s="18"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="18"/>
+      <c r="AS11" s="18"/>
+      <c r="AT11" s="18"/>
+      <c r="AU11" s="18"/>
+      <c r="AV11" s="18"/>
+      <c r="AW11" s="18"/>
+      <c r="AX11" s="18"/>
+      <c r="AY11" s="18"/>
+      <c r="AZ11" s="25" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="BA11" s="20"/>
+      <c r="BA11" s="19"/>
       <c r="BC11" s="9"/>
     </row>
     <row r="12">
@@ -1118,23 +1078,23 @@
         </is>
       </c>
       <c r="N12" s="9"/>
-      <c r="O12" s="28" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t>鑑氏名</t>
         </is>
       </c>
       <c r="P12" s="9"/>
-      <c r="Q12" s="29" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t>資 格</t>
         </is>
       </c>
-      <c r="R12" s="1"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="30" t="inlineStr">
+      <c r="W12" s="27" t="inlineStr">
         <is>
           <t>( )</t>
         </is>
@@ -1179,81 +1139,80 @@
         </is>
       </c>
       <c r="N13" s="9"/>
-      <c r="O13" s="28" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t>提</t>
         </is>
       </c>
       <c r="P13" s="9"/>
-      <c r="Q13" s="31" t="inlineStr">
+      <c r="Q13" s="15" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
       </c>
-      <c r="R13" s="7"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="20"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
       <c r="AA13" s="18"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="20"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="18"/>
       <c r="AG13" s="18"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="20"/>
+      <c r="AH13" s="18"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="18"/>
+      <c r="AL13" s="18"/>
       <c r="AM13" s="18"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="19"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="20"/>
+      <c r="AN13" s="18"/>
+      <c r="AO13" s="18"/>
+      <c r="AP13" s="18"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="18"/>
       <c r="AS13" s="18"/>
-      <c r="AT13" s="19"/>
-      <c r="AU13" s="19"/>
-      <c r="AV13" s="19"/>
-      <c r="AW13" s="19"/>
-      <c r="AX13" s="20"/>
+      <c r="AT13" s="18"/>
+      <c r="AU13" s="18"/>
+      <c r="AV13" s="18"/>
+      <c r="AW13" s="18"/>
+      <c r="AX13" s="18"/>
       <c r="AY13" s="18"/>
-      <c r="AZ13" s="19"/>
-      <c r="BA13" s="20"/>
+      <c r="AZ13" s="18"/>
+      <c r="BA13" s="19"/>
       <c r="BC13" s="9"/>
     </row>
     <row r="14">
       <c r="B14" s="7"/>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>つけてください。)</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="33" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="29" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="4"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -1261,21 +1220,21 @@
       <c r="W14" s="4"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="4"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="4"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="6"/>
-      <c r="AM14" s="4"/>
-      <c r="AN14" s="35" t="inlineStr">
+      <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="30" t="inlineStr">
         <is>
           <t>年</t>
         </is>
@@ -1283,35 +1242,35 @@
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
       <c r="AQ14" s="5"/>
-      <c r="AR14" s="36" t="inlineStr">
+      <c r="AR14" s="30" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AS14" s="4"/>
+      <c r="AS14" s="5"/>
       <c r="AT14" s="5"/>
       <c r="AU14" s="5"/>
       <c r="AV14" s="5"/>
-      <c r="AW14" s="35" t="inlineStr">
+      <c r="AW14" s="30" t="inlineStr">
         <is>
           <t>日生</t>
         </is>
       </c>
-      <c r="AX14" s="6"/>
-      <c r="AY14" s="4"/>
+      <c r="AX14" s="5"/>
+      <c r="AY14" s="5"/>
       <c r="AZ14" s="5"/>
       <c r="BA14" s="6"/>
       <c r="BC14" s="9"/>
     </row>
     <row r="15">
       <c r="B15" s="7"/>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>登記所に提出した</t>
         </is>
@@ -1325,81 +1284,81 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="21" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
       <c r="P15" s="3"/>
-      <c r="Q15" s="38" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
       <c r="R15" s="18"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="26" t="inlineStr">
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="24" t="inlineStr">
         <is>
           <t>大・昭・平・西暦 年 月 日生</t>
         </is>
       </c>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="20"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="18"/>
+      <c r="Z15" s="18"/>
       <c r="AA15" s="18"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="20"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="18"/>
       <c r="AG15" s="18"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="20"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="18"/>
+      <c r="AL15" s="18"/>
       <c r="AM15" s="18"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
-      <c r="AP15" s="19"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="20"/>
+      <c r="AN15" s="18"/>
+      <c r="AO15" s="18"/>
+      <c r="AP15" s="18"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="18"/>
       <c r="AS15" s="18"/>
-      <c r="AT15" s="19"/>
-      <c r="AU15" s="19"/>
-      <c r="AV15" s="19"/>
-      <c r="AW15" s="19"/>
-      <c r="AX15" s="20"/>
+      <c r="AT15" s="18"/>
+      <c r="AU15" s="18"/>
+      <c r="AV15" s="18"/>
+      <c r="AW15" s="18"/>
+      <c r="AX15" s="18"/>
       <c r="AY15" s="18"/>
-      <c r="AZ15" s="19"/>
-      <c r="BA15" s="20"/>
+      <c r="AZ15" s="18"/>
+      <c r="BA15" s="19"/>
       <c r="BC15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="7"/>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>登 記 所 に 提 出 し た</t>
         </is>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="39" t="inlineStr">
+      <c r="D16" s="18"/>
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>印鑑の押印欄印鑑カード番号</t>
         </is>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
@@ -1443,7 +1402,7 @@
     </row>
     <row r="17">
       <c r="B17" s="7"/>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>印 鑑 の 押 印 欄</t>
         </is>
@@ -1459,75 +1418,75 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="26" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>印鑑カード番号</t>
         </is>
       </c>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="40" t="inlineStr">
+      <c r="P17" s="18"/>
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t>カード廃止の理由</t>
         </is>
       </c>
       <c r="R17" s="18"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="32" t="inlineStr">
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="28" t="inlineStr">
         <is>
           <t>亡失（なくなった）</t>
         </is>
       </c>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
-      <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="19"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="19"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="32" t="inlineStr">
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="18"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="18"/>
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="18"/>
+      <c r="AN17" s="18"/>
+      <c r="AO17" s="18"/>
+      <c r="AP17" s="18"/>
+      <c r="AQ17" s="18"/>
+      <c r="AR17" s="28" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AS17" s="19"/>
-      <c r="AT17" s="19"/>
-      <c r="AU17" s="19"/>
-      <c r="AV17" s="19"/>
-      <c r="AW17" s="19"/>
-      <c r="AX17" s="19"/>
-      <c r="AY17" s="19"/>
-      <c r="AZ17" s="19"/>
-      <c r="BA17" s="20"/>
+      <c r="AS17" s="18"/>
+      <c r="AT17" s="18"/>
+      <c r="AU17" s="18"/>
+      <c r="AV17" s="18"/>
+      <c r="AW17" s="18"/>
+      <c r="AX17" s="18"/>
+      <c r="AY17" s="18"/>
+      <c r="AZ17" s="18"/>
+      <c r="BA17" s="19"/>
       <c r="BC17" s="9"/>
     </row>
     <row r="18">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="41" t="inlineStr">
+      <c r="O18" s="33" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、</t>
         </is>
       </c>
       <c r="P18" s="5"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="4"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -1578,7 +1537,7 @@
           <t>※カードのみを廃止する場合に、 汚損（著しく汚れた)</t>
         </is>
       </c>
-      <c r="Q19" s="42" t="inlineStr">
+      <c r="Q19" s="34" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。</t>
         </is>
@@ -1595,75 +1554,74 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="26" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。 き損（破損した）</t>
         </is>
       </c>
-      <c r="P20" s="27" t="inlineStr">
+      <c r="P20" s="25" t="inlineStr">
         <is>
           <t>申請人（注２）</t>
         </is>
       </c>
-      <c r="Q20" s="20"/>
+      <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="20"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
       <c r="Y20" s="18"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="27" t="inlineStr">
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="25" t="inlineStr">
         <is>
           <t>印鑑提出者本人代理人</t>
         </is>
       </c>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="19"/>
-      <c r="AG20" s="19"/>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="19"/>
-      <c r="AQ20" s="19"/>
-      <c r="AR20" s="19"/>
-      <c r="AS20" s="19"/>
-      <c r="AT20" s="19"/>
-      <c r="AU20" s="19"/>
-      <c r="AV20" s="19"/>
-      <c r="AW20" s="19"/>
-      <c r="AX20" s="19"/>
-      <c r="AY20" s="19"/>
-      <c r="AZ20" s="19"/>
-      <c r="BA20" s="20"/>
-      <c r="BB20" s="19"/>
-      <c r="BC20" s="20"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="18"/>
+      <c r="AG20" s="18"/>
+      <c r="AH20" s="18"/>
+      <c r="AI20" s="18"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="18"/>
+      <c r="AL20" s="18"/>
+      <c r="AM20" s="18"/>
+      <c r="AN20" s="18"/>
+      <c r="AO20" s="18"/>
+      <c r="AP20" s="18"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="18"/>
+      <c r="AS20" s="18"/>
+      <c r="AT20" s="18"/>
+      <c r="AU20" s="18"/>
+      <c r="AV20" s="18"/>
+      <c r="AW20" s="18"/>
+      <c r="AX20" s="18"/>
+      <c r="AY20" s="18"/>
+      <c r="AZ20" s="18"/>
+      <c r="BA20" s="19"/>
+      <c r="BC20" s="9"/>
     </row>
     <row r="21">
       <c r="B21" s="7"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="21" t="inlineStr">
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>申 請 人（注２） 印鑑提出者本人 代理人</t>
         </is>
@@ -1710,13 +1668,12 @@
       <c r="AY21" s="2"/>
       <c r="AZ21" s="2"/>
       <c r="BA21" s="3"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="6"/>
+      <c r="BC21" s="9"/>
     </row>
     <row r="22">
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="37" t="inlineStr">
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>（印鑑は鮮明に押</t>
         </is>
@@ -1736,39 +1693,36 @@
           <t>住 所</t>
         </is>
       </c>
-      <c r="Q22" s="43" t="inlineStr">
+      <c r="Q22" s="35" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="R22" s="7"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="7"/>
       <c r="BC22" s="9"/>
     </row>
     <row r="23">
       <c r="B23" s="7"/>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>（ 印 鑑 は 鮮 明 に 押</t>
         </is>
       </c>
-      <c r="D23" s="39" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>印してください。）氏名</t>
         </is>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="21" t="inlineStr">
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
@@ -1815,7 +1769,7 @@
     </row>
     <row r="24">
       <c r="B24" s="7"/>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>印 し て く だ さ い 。 ）</t>
         </is>
@@ -1831,7 +1785,7 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
-      <c r="O24" s="44" t="inlineStr">
+      <c r="O24" s="36" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
@@ -1909,7 +1863,7 @@
         </is>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="45" t="inlineStr">
+      <c r="H26" s="37" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
@@ -1935,7 +1889,7 @@
           <t>私は、（住所）</t>
         </is>
       </c>
-      <c r="J27" s="46" t="inlineStr">
+      <c r="J27" s="38" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
@@ -2019,17 +1973,11 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="W31" s="9"/>
-      <c r="X31" s="7"/>
-      <c r="AD31" s="9"/>
-      <c r="AE31" s="7"/>
-      <c r="AR31" s="24" t="inlineStr">
+      <c r="AR31" s="22" t="inlineStr">
         <is>
           <t>登記所に提</t>
         </is>
       </c>
-      <c r="AY31" s="9"/>
-      <c r="AZ31" s="7"/>
       <c r="BA31" s="9"/>
       <c r="BC31" s="9"/>
     </row>
@@ -2040,22 +1988,16 @@
           <t>登 記 所 に 提</t>
         </is>
       </c>
-      <c r="W32" s="9"/>
-      <c r="X32" s="7"/>
-      <c r="AD32" s="9"/>
-      <c r="AE32" s="7"/>
       <c r="AN32" s="10" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AR32" s="24" t="inlineStr">
+      <c r="AR32" s="22" t="inlineStr">
         <is>
           <t>出した印鑑</t>
         </is>
       </c>
-      <c r="AY32" s="9"/>
-      <c r="AZ32" s="7"/>
       <c r="BA32" s="9"/>
       <c r="BC32" s="9"/>
     </row>
@@ -2066,7 +2008,7 @@
           <t>氏 名</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>（注１）登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
@@ -2086,7 +2028,7 @@
           <t>印</t>
         </is>
       </c>
-      <c r="H34" s="24" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
@@ -2101,7 +2043,7 @@
           <t>出 し た 印 鑑</t>
         </is>
       </c>
-      <c r="H35" s="24" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）は、□にレ印をつけてください。</t>
         </is>
@@ -2116,7 +2058,7 @@
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>（注２）事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
@@ -2131,7 +2073,7 @@
           <t>（注１） 登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
-      <c r="I37" s="24" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
         </is>
@@ -2146,12 +2088,12 @@
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>（注３）村長の証明した印鑑証明書を添付してください。印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
       </c>
-      <c r="Z38" s="22"/>
+      <c r="Z38" s="39"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
@@ -2188,13 +2130,13 @@
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
         </is>
       </c>
-      <c r="I39" s="24" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合</t>
         </is>
       </c>
       <c r="Z39" s="4"/>
-      <c r="AA39" s="44" t="inlineStr">
+      <c r="AA39" s="36" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
@@ -2207,7 +2149,7 @@
       <c r="AG39" s="5"/>
       <c r="AH39" s="5"/>
       <c r="AI39" s="6"/>
-      <c r="AJ39" s="30" t="inlineStr">
+      <c r="AJ39" s="27" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
@@ -2215,7 +2157,7 @@
       <c r="AK39" s="5"/>
       <c r="AL39" s="5"/>
       <c r="AM39" s="6"/>
-      <c r="AN39" s="30" t="inlineStr">
+      <c r="AN39" s="27" t="inlineStr">
         <is>
           <t>調 査</t>
         </is>
@@ -2224,7 +2166,7 @@
       <c r="AP39" s="5"/>
       <c r="AQ39" s="5"/>
       <c r="AR39" s="6"/>
-      <c r="AS39" s="30" t="inlineStr">
+      <c r="AS39" s="27" t="inlineStr">
         <is>
           <t>入 力</t>
         </is>
@@ -2232,7 +2174,7 @@
       <c r="AT39" s="5"/>
       <c r="AU39" s="5"/>
       <c r="AV39" s="6"/>
-      <c r="AW39" s="30" t="inlineStr">
+      <c r="AW39" s="27" t="inlineStr">
         <is>
           <t>校 合</t>
         </is>
@@ -2245,76 +2187,75 @@
     </row>
     <row r="40">
       <c r="B40" s="7"/>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>は、□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="47" t="inlineStr">
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="40" t="inlineStr">
         <is>
           <t>には、(注１)の押印及び(注２)の委任状は不要です。</t>
         </is>
       </c>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19"/>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="19"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
-      <c r="AC40" s="19"/>
-      <c r="AD40" s="19"/>
-      <c r="AE40" s="19"/>
-      <c r="AF40" s="19"/>
-      <c r="AG40" s="19"/>
-      <c r="AH40" s="19"/>
-      <c r="AI40" s="20"/>
-      <c r="AJ40" s="18"/>
-      <c r="AK40" s="19"/>
-      <c r="AL40" s="19"/>
-      <c r="AM40" s="20"/>
-      <c r="AN40" s="18"/>
-      <c r="AO40" s="19"/>
-      <c r="AP40" s="19"/>
-      <c r="AQ40" s="19"/>
-      <c r="AR40" s="20"/>
-      <c r="AS40" s="18"/>
-      <c r="AT40" s="20"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="18"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="18"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="18"/>
+      <c r="AI40" s="19"/>
+      <c r="AJ40" s="17"/>
+      <c r="AK40" s="18"/>
+      <c r="AL40" s="18"/>
+      <c r="AM40" s="19"/>
+      <c r="AN40" s="17"/>
+      <c r="AO40" s="18"/>
+      <c r="AP40" s="18"/>
+      <c r="AQ40" s="18"/>
+      <c r="AR40" s="19"/>
+      <c r="AS40" s="17"/>
+      <c r="AT40" s="18"/>
       <c r="AU40" s="18"/>
-      <c r="AV40" s="20"/>
-      <c r="AW40" s="18"/>
-      <c r="AX40" s="20"/>
+      <c r="AV40" s="19"/>
+      <c r="AW40" s="17"/>
+      <c r="AX40" s="18"/>
       <c r="AY40" s="18"/>
-      <c r="AZ40" s="20"/>
-      <c r="BA40" s="17"/>
-      <c r="BB40" s="9"/>
-      <c r="BC40" s="48"/>
+      <c r="AZ40" s="18"/>
+      <c r="BA40" s="19"/>
+      <c r="BC40" s="9"/>
     </row>
     <row r="41">
-      <c r="B41" s="18"/>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="B41" s="17"/>
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>（注２） 代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
-      <c r="D41" s="49" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>
@@ -2324,52 +2265,52 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
-      <c r="Z41" s="19"/>
-      <c r="AA41" s="19"/>
-      <c r="AB41" s="19"/>
-      <c r="AC41" s="19"/>
-      <c r="AD41" s="19"/>
-      <c r="AE41" s="19"/>
-      <c r="AF41" s="19"/>
-      <c r="AG41" s="19"/>
-      <c r="AH41" s="19"/>
-      <c r="AI41" s="19"/>
-      <c r="AJ41" s="19"/>
-      <c r="AK41" s="19"/>
-      <c r="AL41" s="19"/>
-      <c r="AM41" s="19"/>
-      <c r="AN41" s="19"/>
-      <c r="AO41" s="19"/>
-      <c r="AP41" s="19"/>
-      <c r="AQ41" s="19"/>
-      <c r="AR41" s="20"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="18"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
+      <c r="AF41" s="18"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="18"/>
+      <c r="AI41" s="18"/>
+      <c r="AJ41" s="18"/>
+      <c r="AK41" s="18"/>
+      <c r="AL41" s="18"/>
+      <c r="AM41" s="18"/>
+      <c r="AN41" s="18"/>
+      <c r="AO41" s="18"/>
+      <c r="AP41" s="18"/>
+      <c r="AQ41" s="18"/>
+      <c r="AR41" s="18"/>
       <c r="AS41" s="18"/>
-      <c r="AT41" s="20"/>
+      <c r="AT41" s="18"/>
       <c r="AU41" s="18"/>
-      <c r="AV41" s="20"/>
+      <c r="AV41" s="18"/>
       <c r="AW41" s="18"/>
-      <c r="AX41" s="20"/>
+      <c r="AX41" s="18"/>
       <c r="AY41" s="18"/>
-      <c r="AZ41" s="20"/>
+      <c r="AZ41" s="18"/>
       <c r="BA41" s="18"/>
-      <c r="BB41" s="20"/>
-      <c r="BC41" s="17"/>
+      <c r="BB41" s="18"/>
+      <c r="BC41" s="19"/>
     </row>
     <row r="42">
       <c r="C42" s="15" t="inlineStr">

--- a/data/out/test1/001328648_Python版_1pt.xlsx
+++ b/data/out/test1/001328648_Python版_1pt.xlsx
@@ -1961,7 +1961,7 @@
     <row r="25">
       <c r="B25" s="4"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -2022,6 +2022,14 @@
     <row r="26">
       <c r="B26" s="4"/>
       <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
       <c r="AA26" s="17" t="inlineStr">
         <is>
           <t>委</t>
@@ -2044,6 +2052,7 @@
     <row r="27">
       <c r="B27" s="4"/>
       <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
       <c r="H27" s="39" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
@@ -2068,6 +2077,7 @@
     <row r="28">
       <c r="B28" s="4"/>
       <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
       <c r="K28" s="11" t="inlineStr">
         <is>
           <t>（氏名）</t>
@@ -2085,6 +2095,7 @@
     <row r="29">
       <c r="B29" s="4"/>
       <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
           <t>を代理人と定め、印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
@@ -2097,6 +2108,7 @@
     <row r="30">
       <c r="B30" s="4"/>
       <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
           <t>の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。</t>
@@ -2109,6 +2121,7 @@
     <row r="31">
       <c r="B31" s="4"/>
       <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
       <c r="O31" s="17" t="inlineStr">
         <is>
           <t>年</t>
@@ -2131,6 +2144,7 @@
     <row r="32">
       <c r="B32" s="4"/>
       <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
       <c r="I32" s="17" t="inlineStr">
         <is>
           <t>住所</t>
@@ -2143,6 +2157,7 @@
     <row r="33">
       <c r="B33" s="4"/>
       <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
       <c r="I33" s="17" t="inlineStr">
         <is>
           <t>氏名</t>
@@ -2165,6 +2180,7 @@
     <row r="34">
       <c r="B34" s="4"/>
       <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
       <c r="G34" s="17" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
@@ -2177,7 +2193,7 @@
     <row r="35">
       <c r="B35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="40" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>（注１）の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み登</t>
         </is>
@@ -2189,6 +2205,7 @@
     <row r="36">
       <c r="B36" s="4"/>
       <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="I36" s="40" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
@@ -2201,7 +2218,7 @@
     <row r="37">
       <c r="B37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="40" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>（注２）は、□にレ印をつけてください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
@@ -2213,6 +2230,7 @@
     <row r="38">
       <c r="B38" s="4"/>
       <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
       <c r="I38" s="40" t="inlineStr">
         <is>
           <t>事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。</t>
@@ -2225,6 +2243,7 @@
     <row r="39">
       <c r="B39" s="4"/>
       <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
       <c r="I39" s="40" t="inlineStr">
         <is>
           <t>村長の証明した印鑑証明書を添付してください。この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
@@ -2237,7 +2256,7 @@
     <row r="40">
       <c r="B40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>（注３）印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
@@ -2299,43 +2318,66 @@
     <row r="41">
       <c r="B41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="I41" s="40" t="inlineStr">
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="41" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合には、(注１)の押印及び(注２)の委</t>
         </is>
       </c>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="2"/>
-      <c r="AE41" s="2"/>
-      <c r="AF41" s="2"/>
-      <c r="AG41" s="2"/>
-      <c r="AH41" s="2"/>
-      <c r="AI41" s="2"/>
-      <c r="AJ41" s="2"/>
-      <c r="AK41" s="2"/>
-      <c r="AL41" s="2"/>
-      <c r="AM41" s="3"/>
-      <c r="AN41" s="1"/>
-      <c r="AO41" s="2"/>
-      <c r="AP41" s="2"/>
-      <c r="AQ41" s="2"/>
-      <c r="AR41" s="3"/>
-      <c r="AS41" s="1"/>
-      <c r="AT41" s="2"/>
-      <c r="AU41" s="2"/>
-      <c r="AV41" s="2"/>
-      <c r="AW41" s="3"/>
-      <c r="AX41" s="1"/>
-      <c r="AY41" s="2"/>
-      <c r="AZ41" s="2"/>
-      <c r="BA41" s="2"/>
-      <c r="BB41" s="3"/>
-      <c r="BC41" s="1"/>
-      <c r="BD41" s="2"/>
-      <c r="BE41" s="2"/>
-      <c r="BF41" s="2"/>
-      <c r="BG41" s="3"/>
-      <c r="BH41" s="38"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="12"/>
+      <c r="AE41" s="12"/>
+      <c r="AF41" s="12"/>
+      <c r="AG41" s="12"/>
+      <c r="AH41" s="12"/>
+      <c r="AI41" s="12"/>
+      <c r="AJ41" s="12"/>
+      <c r="AK41" s="12"/>
+      <c r="AL41" s="12"/>
+      <c r="AM41" s="14"/>
+      <c r="AN41" s="19"/>
+      <c r="AO41" s="12"/>
+      <c r="AP41" s="12"/>
+      <c r="AQ41" s="12"/>
+      <c r="AR41" s="14"/>
+      <c r="AS41" s="19"/>
+      <c r="AT41" s="12"/>
+      <c r="AU41" s="12"/>
+      <c r="AV41" s="12"/>
+      <c r="AW41" s="14"/>
+      <c r="AX41" s="19"/>
+      <c r="AY41" s="12"/>
+      <c r="AZ41" s="12"/>
+      <c r="BA41" s="12"/>
+      <c r="BB41" s="14"/>
+      <c r="BC41" s="19"/>
+      <c r="BD41" s="12"/>
+      <c r="BE41" s="12"/>
+      <c r="BF41" s="12"/>
+      <c r="BG41" s="14"/>
+      <c r="BH41" s="42"/>
       <c r="BI41" s="7"/>
     </row>
     <row r="42">

--- a/data/out/test1/001328648_Python版_1pt.xlsx
+++ b/data/out/test1/001328648_Python版_1pt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$BJ$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$BK$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,49 +178,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -233,27 +240,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -263,7 +261,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -632,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:BI43"/>
+  <dimension ref="B2:BJ43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="1.625" defaultRowHeight="18.25" customHeight="1"/>
   <sheetData>
     <row r="2">
@@ -696,6 +693,7 @@
       <c r="BG2" s="2"/>
       <c r="BH2" s="2"/>
       <c r="BI2" s="3"/>
+      <c r="BJ2" s="4"/>
     </row>
     <row r="3">
       <c r="B3" s="4"/>
@@ -784,92 +782,96 @@
       </c>
       <c r="AX3" s="2"/>
       <c r="AY3" s="2"/>
-      <c r="AZ3" s="3"/>
-      <c r="BI3" s="7"/>
+      <c r="AZ3" s="7"/>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="4"/>
     </row>
     <row r="4">
       <c r="B4" s="4"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
-      <c r="AV4" s="9"/>
-      <c r="AW4" s="9"/>
-      <c r="AX4" s="9"/>
-      <c r="AY4" s="9"/>
-      <c r="AZ4" s="10"/>
-      <c r="BI4" s="7"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="10"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="10"/>
+      <c r="AO4" s="10"/>
+      <c r="AP4" s="10"/>
+      <c r="AQ4" s="10"/>
+      <c r="AR4" s="10"/>
+      <c r="AS4" s="10"/>
+      <c r="AT4" s="10"/>
+      <c r="AU4" s="10"/>
+      <c r="AV4" s="10"/>
+      <c r="AW4" s="10"/>
+      <c r="AX4" s="10"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="11"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="4"/>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>※</t>
         </is>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="13" t="inlineStr">
         <is>
           <t>太枠の中に書いてください。</t>
         </is>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="14"/>
-      <c r="BI5" s="7"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="11"/>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="4"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>（地方）法務局</t>
         </is>
@@ -879,7 +881,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="3"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -889,7 +891,7 @@
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="16" t="inlineStr">
+      <c r="Z6" s="15" t="inlineStr">
         <is>
           <t>支局・出張所</t>
         </is>
@@ -902,13 +904,13 @@
       <c r="AF6" s="2"/>
       <c r="AG6" s="2"/>
       <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
+      <c r="AI6" s="1"/>
       <c r="AJ6" s="2"/>
       <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
-      <c r="AO6" s="15" t="inlineStr">
+      <c r="AO6" s="14" t="inlineStr">
         <is>
           <t>年</t>
         </is>
@@ -917,7 +919,7 @@
       <c r="AQ6" s="2"/>
       <c r="AR6" s="2"/>
       <c r="AS6" s="2"/>
-      <c r="AT6" s="15" t="inlineStr">
+      <c r="AT6" s="14" t="inlineStr">
         <is>
           <t>月</t>
         </is>
@@ -926,13 +928,13 @@
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
-      <c r="AY6" s="15" t="inlineStr">
+      <c r="AY6" s="14" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
       <c r="AZ6" s="2"/>
-      <c r="BA6" s="15" t="inlineStr">
+      <c r="BA6" s="14" t="inlineStr">
         <is>
           <t>届出</t>
         </is>
@@ -943,472 +945,526 @@
       <c r="BE6" s="2"/>
       <c r="BF6" s="2"/>
       <c r="BG6" s="3"/>
-      <c r="BI6" s="7"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="8"/>
+      <c r="BJ6" s="4"/>
     </row>
     <row r="7">
       <c r="B7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
       </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
       <c r="P7" s="7"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="Q7" s="9"/>
+      <c r="R7" s="17" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
       </c>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
-      <c r="AJ7" s="9"/>
-      <c r="AK7" s="9"/>
-      <c r="AL7" s="9"/>
-      <c r="AM7" s="9"/>
-      <c r="AN7" s="9"/>
-      <c r="AO7" s="9"/>
-      <c r="AP7" s="9"/>
-      <c r="AQ7" s="9"/>
-      <c r="AR7" s="9"/>
-      <c r="AS7" s="9"/>
-      <c r="AT7" s="9"/>
-      <c r="AU7" s="9"/>
-      <c r="AV7" s="9"/>
-      <c r="AW7" s="9"/>
-      <c r="AX7" s="9"/>
-      <c r="AY7" s="9"/>
-      <c r="AZ7" s="9"/>
-      <c r="BA7" s="9"/>
-      <c r="BB7" s="9"/>
-      <c r="BC7" s="9"/>
-      <c r="BD7" s="9"/>
-      <c r="BE7" s="9"/>
-      <c r="BF7" s="9"/>
-      <c r="BG7" s="10"/>
-      <c r="BI7" s="7"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="10"/>
+      <c r="AO7" s="10"/>
+      <c r="AP7" s="10"/>
+      <c r="AQ7" s="10"/>
+      <c r="AR7" s="10"/>
+      <c r="AS7" s="10"/>
+      <c r="AT7" s="10"/>
+      <c r="AU7" s="10"/>
+      <c r="AV7" s="10"/>
+      <c r="AW7" s="10"/>
+      <c r="AX7" s="10"/>
+      <c r="AY7" s="10"/>
+      <c r="AZ7" s="10"/>
+      <c r="BA7" s="10"/>
+      <c r="BB7" s="10"/>
+      <c r="BC7" s="10"/>
+      <c r="BD7" s="10"/>
+      <c r="BE7" s="10"/>
+      <c r="BF7" s="10"/>
+      <c r="BG7" s="18"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="4"/>
     </row>
     <row r="8">
       <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-      <c r="BC8" s="12"/>
-      <c r="BD8" s="12"/>
-      <c r="BE8" s="12"/>
-      <c r="BF8" s="12"/>
-      <c r="BG8" s="14"/>
-      <c r="BH8" s="14"/>
-      <c r="BI8" s="7"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="10"/>
+      <c r="AK8" s="10"/>
+      <c r="AL8" s="10"/>
+      <c r="AM8" s="10"/>
+      <c r="AN8" s="10"/>
+      <c r="AO8" s="10"/>
+      <c r="AP8" s="10"/>
+      <c r="AQ8" s="10"/>
+      <c r="AR8" s="10"/>
+      <c r="AS8" s="10"/>
+      <c r="AT8" s="10"/>
+      <c r="AU8" s="10"/>
+      <c r="AV8" s="10"/>
+      <c r="AW8" s="10"/>
+      <c r="AX8" s="10"/>
+      <c r="AY8" s="10"/>
+      <c r="AZ8" s="10"/>
+      <c r="BA8" s="10"/>
+      <c r="BB8" s="10"/>
+      <c r="BC8" s="10"/>
+      <c r="BD8" s="10"/>
+      <c r="BE8" s="10"/>
+      <c r="BF8" s="10"/>
+      <c r="BG8" s="18"/>
+      <c r="BH8" s="11"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="4"/>
     </row>
     <row r="9">
       <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー廃止届出</t>
         </is>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="20" t="inlineStr">
+      <c r="P9" s="20"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="9"/>
-      <c r="AJ9" s="9"/>
-      <c r="AK9" s="9"/>
-      <c r="AL9" s="9"/>
-      <c r="AM9" s="9"/>
-      <c r="AN9" s="9"/>
-      <c r="AO9" s="9"/>
-      <c r="AP9" s="9"/>
-      <c r="AQ9" s="9"/>
-      <c r="AR9" s="9"/>
-      <c r="AS9" s="9"/>
-      <c r="AT9" s="9"/>
-      <c r="AU9" s="9"/>
-      <c r="AV9" s="9"/>
-      <c r="AW9" s="9"/>
-      <c r="AX9" s="9"/>
-      <c r="AY9" s="9"/>
-      <c r="AZ9" s="9"/>
-      <c r="BA9" s="9"/>
-      <c r="BB9" s="9"/>
-      <c r="BC9" s="9"/>
-      <c r="BD9" s="9"/>
-      <c r="BE9" s="9"/>
-      <c r="BF9" s="9"/>
-      <c r="BG9" s="10"/>
-      <c r="BI9" s="7"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="22"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="22"/>
+      <c r="AM9" s="22"/>
+      <c r="AN9" s="22"/>
+      <c r="AO9" s="22"/>
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="22"/>
+      <c r="AV9" s="22"/>
+      <c r="AW9" s="22"/>
+      <c r="AX9" s="22"/>
+      <c r="AY9" s="22"/>
+      <c r="AZ9" s="22"/>
+      <c r="BA9" s="22"/>
+      <c r="BB9" s="22"/>
+      <c r="BC9" s="22"/>
+      <c r="BD9" s="22"/>
+      <c r="BE9" s="22"/>
+      <c r="BF9" s="22"/>
+      <c r="BG9" s="23"/>
+      <c r="BH9" s="4"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="4"/>
     </row>
     <row r="10">
       <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="11" t="inlineStr">
+      <c r="P10" s="20"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="18"/>
+      <c r="Z10" s="12" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
       </c>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12"/>
-      <c r="AY10" s="12"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="12"/>
-      <c r="BD10" s="12"/>
-      <c r="BE10" s="12"/>
-      <c r="BF10" s="12"/>
-      <c r="BG10" s="14"/>
-      <c r="BH10" s="14"/>
-      <c r="BI10" s="7"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="10"/>
+      <c r="AO10" s="10"/>
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="10"/>
+      <c r="AS10" s="10"/>
+      <c r="AT10" s="10"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="10"/>
+      <c r="AW10" s="10"/>
+      <c r="AX10" s="10"/>
+      <c r="AY10" s="10"/>
+      <c r="AZ10" s="10"/>
+      <c r="BA10" s="10"/>
+      <c r="BB10" s="10"/>
+      <c r="BC10" s="10"/>
+      <c r="BD10" s="10"/>
+      <c r="BE10" s="10"/>
+      <c r="BF10" s="10"/>
+      <c r="BG10" s="18"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="8"/>
+      <c r="BJ10" s="4"/>
     </row>
     <row r="11">
       <c r="B11" s="4"/>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="C11" s="4"/>
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印を</t>
         </is>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="22" t="inlineStr">
+      <c r="P11" s="20"/>
+      <c r="Q11" s="25" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="R11" s="3"/>
-      <c r="T11" s="23" t="inlineStr">
+      <c r="R11" s="7"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="26" t="inlineStr">
         <is>
           <t>資格</t>
         </is>
       </c>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="18" t="inlineStr">
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="28" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="9"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="9"/>
-      <c r="AJ11" s="9"/>
-      <c r="AK11" s="9"/>
-      <c r="AL11" s="9"/>
-      <c r="AM11" s="9"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="9"/>
-      <c r="AP11" s="9"/>
-      <c r="AQ11" s="9"/>
-      <c r="AR11" s="9"/>
-      <c r="AS11" s="9"/>
-      <c r="AT11" s="9"/>
-      <c r="AU11" s="9"/>
-      <c r="AV11" s="9"/>
-      <c r="AW11" s="9"/>
-      <c r="AX11" s="9"/>
-      <c r="AY11" s="9"/>
-      <c r="AZ11" s="9"/>
-      <c r="BA11" s="9"/>
-      <c r="BB11" s="9"/>
-      <c r="BC11" s="9"/>
-      <c r="BD11" s="9"/>
-      <c r="BE11" s="18" t="inlineStr">
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="22"/>
+      <c r="AH11" s="22"/>
+      <c r="AI11" s="22"/>
+      <c r="AJ11" s="22"/>
+      <c r="AK11" s="22"/>
+      <c r="AL11" s="22"/>
+      <c r="AM11" s="22"/>
+      <c r="AN11" s="22"/>
+      <c r="AO11" s="22"/>
+      <c r="AP11" s="22"/>
+      <c r="AQ11" s="22"/>
+      <c r="AR11" s="22"/>
+      <c r="AS11" s="22"/>
+      <c r="AT11" s="22"/>
+      <c r="AU11" s="22"/>
+      <c r="AV11" s="22"/>
+      <c r="AW11" s="22"/>
+      <c r="AX11" s="22"/>
+      <c r="AY11" s="22"/>
+      <c r="AZ11" s="22"/>
+      <c r="BA11" s="22"/>
+      <c r="BB11" s="22"/>
+      <c r="BC11" s="22"/>
+      <c r="BD11" s="22"/>
+      <c r="BE11" s="28" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="BF11" s="9"/>
-      <c r="BG11" s="10"/>
-      <c r="BI11" s="7"/>
+      <c r="BF11" s="22"/>
+      <c r="BG11" s="23"/>
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="8"/>
+      <c r="BJ11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="4"/>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="C12" s="4"/>
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>つけてください。)</t>
         </is>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="P12" s="20"/>
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t>鑑</t>
         </is>
       </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="24" t="inlineStr">
+      <c r="R12" s="20"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="26" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="12"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-      <c r="BC12" s="12"/>
-      <c r="BD12" s="12"/>
-      <c r="BE12" s="12"/>
-      <c r="BF12" s="12"/>
-      <c r="BG12" s="14"/>
-      <c r="BH12" s="14"/>
-      <c r="BI12" s="7"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="10"/>
+      <c r="AO12" s="10"/>
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10"/>
+      <c r="AR12" s="10"/>
+      <c r="AS12" s="10"/>
+      <c r="AT12" s="10"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="10"/>
+      <c r="AW12" s="10"/>
+      <c r="AX12" s="10"/>
+      <c r="AY12" s="10"/>
+      <c r="AZ12" s="10"/>
+      <c r="BA12" s="10"/>
+      <c r="BB12" s="10"/>
+      <c r="BC12" s="10"/>
+      <c r="BD12" s="10"/>
+      <c r="BE12" s="10"/>
+      <c r="BF12" s="10"/>
+      <c r="BG12" s="18"/>
+      <c r="BH12" s="11"/>
+      <c r="BI12" s="8"/>
+      <c r="BJ12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="21" t="inlineStr">
+      <c r="P13" s="20"/>
+      <c r="Q13" s="24" t="inlineStr">
         <is>
           <t>提</t>
         </is>
       </c>
-      <c r="R13" s="7"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="9"/>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="9"/>
-      <c r="AI13" s="9"/>
-      <c r="AJ13" s="9"/>
-      <c r="AK13" s="9"/>
-      <c r="AL13" s="9"/>
-      <c r="AM13" s="9"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="9"/>
-      <c r="AP13" s="9"/>
-      <c r="AQ13" s="9"/>
-      <c r="AR13" s="9"/>
-      <c r="AS13" s="9"/>
-      <c r="AT13" s="9"/>
-      <c r="AU13" s="9"/>
-      <c r="AV13" s="9"/>
-      <c r="AW13" s="9"/>
-      <c r="AX13" s="9"/>
-      <c r="AY13" s="9"/>
-      <c r="AZ13" s="9"/>
-      <c r="BA13" s="9"/>
-      <c r="BB13" s="9"/>
-      <c r="BC13" s="9"/>
-      <c r="BD13" s="9"/>
-      <c r="BE13" s="9"/>
-      <c r="BF13" s="9"/>
-      <c r="BG13" s="10"/>
-      <c r="BI13" s="7"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="22"/>
+      <c r="AM13" s="22"/>
+      <c r="AN13" s="22"/>
+      <c r="AO13" s="22"/>
+      <c r="AP13" s="22"/>
+      <c r="AQ13" s="22"/>
+      <c r="AR13" s="22"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="22"/>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="22"/>
+      <c r="AW13" s="22"/>
+      <c r="AX13" s="22"/>
+      <c r="AY13" s="22"/>
+      <c r="AZ13" s="22"/>
+      <c r="BA13" s="22"/>
+      <c r="BB13" s="22"/>
+      <c r="BC13" s="22"/>
+      <c r="BD13" s="22"/>
+      <c r="BE13" s="22"/>
+      <c r="BF13" s="22"/>
+      <c r="BG13" s="23"/>
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="4"/>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="C14" s="4"/>
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="26" t="inlineStr">
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="31" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="R14" s="10"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="12"/>
-      <c r="AY14" s="12"/>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12"/>
-      <c r="BC14" s="12"/>
-      <c r="BD14" s="12"/>
-      <c r="BE14" s="12"/>
-      <c r="BF14" s="12"/>
-      <c r="BG14" s="14"/>
-      <c r="BH14" s="14"/>
-      <c r="BI14" s="7"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="18"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="10"/>
+      <c r="AN14" s="10"/>
+      <c r="AO14" s="10"/>
+      <c r="AP14" s="10"/>
+      <c r="AQ14" s="10"/>
+      <c r="AR14" s="10"/>
+      <c r="AS14" s="10"/>
+      <c r="AT14" s="10"/>
+      <c r="AU14" s="10"/>
+      <c r="AV14" s="10"/>
+      <c r="AW14" s="10"/>
+      <c r="AX14" s="10"/>
+      <c r="AY14" s="10"/>
+      <c r="AZ14" s="10"/>
+      <c r="BA14" s="10"/>
+      <c r="BB14" s="10"/>
+      <c r="BC14" s="10"/>
+      <c r="BD14" s="10"/>
+      <c r="BE14" s="10"/>
+      <c r="BF14" s="10"/>
+      <c r="BG14" s="18"/>
+      <c r="BH14" s="11"/>
+      <c r="BI14" s="8"/>
+      <c r="BJ14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1421,143 +1477,148 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="27" t="inlineStr">
+      <c r="P15" s="7"/>
+      <c r="Q15" s="32" t="inlineStr">
         <is>
           <t>者</t>
         </is>
       </c>
-      <c r="R15" s="14"/>
-      <c r="S15" s="28" t="inlineStr">
+      <c r="R15" s="11"/>
+      <c r="S15" s="33" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="18" t="inlineStr">
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="28" t="inlineStr">
         <is>
           <t>大・昭・平・西暦</t>
         </is>
       </c>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="9"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="9"/>
-      <c r="AI15" s="9"/>
-      <c r="AJ15" s="9"/>
-      <c r="AK15" s="9"/>
-      <c r="AL15" s="9"/>
-      <c r="AM15" s="9"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="9"/>
-      <c r="AP15" s="9"/>
-      <c r="AQ15" s="9"/>
-      <c r="AR15" s="18" t="inlineStr">
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="22"/>
+      <c r="AH15" s="22"/>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="22"/>
+      <c r="AM15" s="22"/>
+      <c r="AN15" s="22"/>
+      <c r="AO15" s="22"/>
+      <c r="AP15" s="22"/>
+      <c r="AQ15" s="22"/>
+      <c r="AR15" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="AS15" s="9"/>
-      <c r="AT15" s="9"/>
-      <c r="AU15" s="9"/>
-      <c r="AV15" s="9"/>
-      <c r="AW15" s="18" t="inlineStr">
+      <c r="AS15" s="22"/>
+      <c r="AT15" s="22"/>
+      <c r="AU15" s="22"/>
+      <c r="AV15" s="22"/>
+      <c r="AW15" s="28" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AX15" s="9"/>
-      <c r="AY15" s="9"/>
-      <c r="AZ15" s="9"/>
-      <c r="BA15" s="9"/>
-      <c r="BB15" s="18" t="inlineStr">
+      <c r="AX15" s="22"/>
+      <c r="AY15" s="22"/>
+      <c r="AZ15" s="22"/>
+      <c r="BA15" s="22"/>
+      <c r="BB15" s="28" t="inlineStr">
         <is>
           <t>日生</t>
         </is>
       </c>
-      <c r="BC15" s="9"/>
-      <c r="BD15" s="9"/>
-      <c r="BE15" s="9"/>
-      <c r="BF15" s="9"/>
-      <c r="BG15" s="10"/>
-      <c r="BI15" s="7"/>
+      <c r="BC15" s="22"/>
+      <c r="BD15" s="22"/>
+      <c r="BE15" s="22"/>
+      <c r="BF15" s="22"/>
+      <c r="BG15" s="23"/>
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="8"/>
+      <c r="BJ15" s="4"/>
     </row>
     <row r="16">
       <c r="B16" s="4"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="C16" s="4"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>登印記鑑所のに提押出印し欄た</t>
         </is>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
-      <c r="AB16" s="12"/>
-      <c r="AC16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="12"/>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="12"/>
-      <c r="AK16" s="12"/>
-      <c r="AL16" s="12"/>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
-      <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-      <c r="BC16" s="12"/>
-      <c r="BD16" s="12"/>
-      <c r="BE16" s="12"/>
-      <c r="BF16" s="12"/>
-      <c r="BG16" s="14"/>
-      <c r="BH16" s="14"/>
-      <c r="BI16" s="7"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="10"/>
+      <c r="AN16" s="10"/>
+      <c r="AO16" s="10"/>
+      <c r="AP16" s="10"/>
+      <c r="AQ16" s="10"/>
+      <c r="AR16" s="10"/>
+      <c r="AS16" s="10"/>
+      <c r="AT16" s="10"/>
+      <c r="AU16" s="10"/>
+      <c r="AV16" s="10"/>
+      <c r="AW16" s="10"/>
+      <c r="AX16" s="10"/>
+      <c r="AY16" s="10"/>
+      <c r="AZ16" s="10"/>
+      <c r="BA16" s="10"/>
+      <c r="BB16" s="10"/>
+      <c r="BC16" s="10"/>
+      <c r="BD16" s="10"/>
+      <c r="BE16" s="10"/>
+      <c r="BF16" s="10"/>
+      <c r="BG16" s="18"/>
+      <c r="BH16" s="11"/>
+      <c r="BI16" s="8"/>
+      <c r="BJ16" s="4"/>
     </row>
     <row r="17">
       <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1570,87 +1631,94 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="P17" s="7"/>
+      <c r="Q17" s="24" t="inlineStr">
         <is>
           <t>印鑑カード番号</t>
         </is>
       </c>
-      <c r="BG17" s="7"/>
-      <c r="BI17" s="7"/>
+      <c r="Z17" s="4"/>
+      <c r="BG17" s="8"/>
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="8"/>
+      <c r="BJ17" s="4"/>
     </row>
     <row r="18">
       <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="28" t="inlineStr">
+      <c r="P18" s="20"/>
+      <c r="Q18" s="17" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、カード廃止の理由</t>
         </is>
       </c>
-      <c r="R18" s="9"/>
+      <c r="R18" s="10"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
       <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
       <c r="AF18" s="9"/>
-      <c r="AG18" s="9"/>
-      <c r="AH18" s="30" t="inlineStr">
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="12" t="inlineStr">
         <is>
           <t>亡失（なくなった）汚損（著しく汚れた)</t>
         </is>
       </c>
-      <c r="AI18" s="9"/>
-      <c r="AJ18" s="9"/>
-      <c r="AK18" s="9"/>
-      <c r="AL18" s="9"/>
-      <c r="AM18" s="9"/>
-      <c r="AN18" s="9"/>
-      <c r="AO18" s="9"/>
-      <c r="AP18" s="9"/>
-      <c r="AQ18" s="9"/>
-      <c r="AR18" s="9"/>
-      <c r="AS18" s="9"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="10"/>
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="10"/>
+      <c r="AS18" s="10"/>
       <c r="AT18" s="9"/>
       <c r="AU18" s="9"/>
-      <c r="AV18" s="9"/>
-      <c r="AW18" s="30" t="inlineStr">
+      <c r="AV18" s="10"/>
+      <c r="AW18" s="12" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AX18" s="9"/>
-      <c r="AY18" s="9"/>
-      <c r="AZ18" s="9"/>
+      <c r="AX18" s="10"/>
+      <c r="AY18" s="10"/>
+      <c r="AZ18" s="10"/>
       <c r="BA18" s="9"/>
-      <c r="BB18" s="9"/>
-      <c r="BC18" s="9"/>
-      <c r="BD18" s="9"/>
-      <c r="BE18" s="9"/>
-      <c r="BF18" s="9"/>
-      <c r="BG18" s="10"/>
-      <c r="BI18" s="7"/>
+      <c r="BB18" s="10"/>
+      <c r="BC18" s="10"/>
+      <c r="BD18" s="10"/>
+      <c r="BE18" s="10"/>
+      <c r="BF18" s="10"/>
+      <c r="BG18" s="18"/>
+      <c r="BH18" s="1"/>
+      <c r="BI18" s="8"/>
+      <c r="BJ18" s="4"/>
     </row>
     <row r="19">
       <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="P19" s="7"/>
+      <c r="P19" s="20"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="31" t="inlineStr">
+      <c r="R19" s="35" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="S19" s="2"/>
+      <c r="S19" s="1"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -1663,9 +1731,9 @@
       <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
       <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
+      <c r="AF19" s="1"/>
       <c r="AG19" s="2"/>
-      <c r="AH19" s="32" t="inlineStr">
+      <c r="AH19" s="36" t="inlineStr">
         <is>
           <t>き損（破損した）</t>
         </is>
@@ -1680,143 +1748,151 @@
       <c r="AP19" s="2"/>
       <c r="AQ19" s="2"/>
       <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-      <c r="AU19" s="2"/>
+      <c r="AS19" s="1"/>
+      <c r="AT19" s="1"/>
+      <c r="AU19" s="1"/>
       <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
+      <c r="AW19" s="1"/>
       <c r="AX19" s="2"/>
       <c r="AY19" s="2"/>
       <c r="AZ19" s="2"/>
-      <c r="BA19" s="2"/>
+      <c r="BA19" s="1"/>
       <c r="BB19" s="2"/>
       <c r="BC19" s="2"/>
       <c r="BD19" s="2"/>
       <c r="BE19" s="2"/>
       <c r="BF19" s="2"/>
       <c r="BG19" s="3"/>
-      <c r="BI19" s="7"/>
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="8"/>
+      <c r="BJ19" s="4"/>
     </row>
     <row r="20">
       <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="28" t="inlineStr">
+      <c r="P20" s="20"/>
+      <c r="Q20" s="17" t="inlineStr">
         <is>
           <t>申請人（注２）</t>
         </is>
       </c>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
       <c r="AF20" s="9"/>
-      <c r="AG20" s="18" t="inlineStr">
+      <c r="AG20" s="26" t="inlineStr">
         <is>
           <t>印鑑提出者本人代理人</t>
         </is>
       </c>
       <c r="AH20" s="9"/>
-      <c r="AI20" s="9"/>
-      <c r="AJ20" s="9"/>
-      <c r="AK20" s="9"/>
-      <c r="AL20" s="9"/>
-      <c r="AM20" s="9"/>
-      <c r="AN20" s="9"/>
-      <c r="AO20" s="9"/>
-      <c r="AP20" s="9"/>
-      <c r="AQ20" s="9"/>
-      <c r="AR20" s="9"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10"/>
+      <c r="AM20" s="10"/>
+      <c r="AN20" s="10"/>
+      <c r="AO20" s="10"/>
+      <c r="AP20" s="10"/>
+      <c r="AQ20" s="10"/>
+      <c r="AR20" s="10"/>
       <c r="AS20" s="9"/>
-      <c r="AT20" s="9"/>
+      <c r="AT20" s="10"/>
       <c r="AU20" s="9"/>
-      <c r="AV20" s="9"/>
-      <c r="AW20" s="9"/>
-      <c r="AX20" s="9"/>
-      <c r="AY20" s="9"/>
-      <c r="AZ20" s="9"/>
-      <c r="BA20" s="9"/>
-      <c r="BB20" s="9"/>
-      <c r="BC20" s="9"/>
-      <c r="BD20" s="9"/>
-      <c r="BE20" s="9"/>
-      <c r="BF20" s="9"/>
-      <c r="BG20" s="10"/>
-      <c r="BI20" s="7"/>
+      <c r="AV20" s="10"/>
+      <c r="AW20" s="10"/>
+      <c r="AX20" s="10"/>
+      <c r="AY20" s="10"/>
+      <c r="AZ20" s="10"/>
+      <c r="BA20" s="10"/>
+      <c r="BB20" s="10"/>
+      <c r="BC20" s="10"/>
+      <c r="BD20" s="10"/>
+      <c r="BE20" s="10"/>
+      <c r="BF20" s="10"/>
+      <c r="BG20" s="18"/>
+      <c r="BH20" s="11"/>
+      <c r="BI20" s="8"/>
+      <c r="BJ20" s="4"/>
     </row>
     <row r="21">
       <c r="B21" s="4"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
-      <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="12"/>
-      <c r="AE21" s="12"/>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="12"/>
-      <c r="AI21" s="12"/>
-      <c r="AJ21" s="12"/>
-      <c r="AK21" s="12"/>
-      <c r="AL21" s="12"/>
-      <c r="AM21" s="12"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="12"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="12"/>
-      <c r="AT21" s="12"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="12"/>
-      <c r="AX21" s="12"/>
-      <c r="AY21" s="12"/>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-      <c r="BC21" s="12"/>
-      <c r="BD21" s="12"/>
-      <c r="BE21" s="12"/>
-      <c r="BF21" s="12"/>
-      <c r="BG21" s="14"/>
-      <c r="BH21" s="14"/>
-      <c r="BI21" s="7"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="10"/>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="10"/>
+      <c r="AM21" s="10"/>
+      <c r="AN21" s="10"/>
+      <c r="AO21" s="10"/>
+      <c r="AP21" s="10"/>
+      <c r="AQ21" s="10"/>
+      <c r="AR21" s="10"/>
+      <c r="AS21" s="10"/>
+      <c r="AT21" s="10"/>
+      <c r="AU21" s="10"/>
+      <c r="AV21" s="10"/>
+      <c r="AW21" s="10"/>
+      <c r="AX21" s="10"/>
+      <c r="AY21" s="10"/>
+      <c r="AZ21" s="10"/>
+      <c r="BA21" s="10"/>
+      <c r="BB21" s="10"/>
+      <c r="BC21" s="10"/>
+      <c r="BD21" s="10"/>
+      <c r="BE21" s="10"/>
+      <c r="BF21" s="10"/>
+      <c r="BG21" s="18"/>
+      <c r="BH21" s="11"/>
+      <c r="BI21" s="8"/>
+      <c r="BJ21" s="4"/>
     </row>
     <row r="22">
       <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1829,139 +1905,205 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="3"/>
-      <c r="R22" s="23" t="inlineStr">
+      <c r="P22" s="7"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="26" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
-      <c r="AI22" s="9"/>
-      <c r="AJ22" s="9"/>
-      <c r="AK22" s="9"/>
-      <c r="AL22" s="9"/>
-      <c r="AM22" s="9"/>
-      <c r="AN22" s="9"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="9"/>
-      <c r="AQ22" s="9"/>
-      <c r="AR22" s="9"/>
-      <c r="AS22" s="9"/>
-      <c r="AT22" s="9"/>
-      <c r="AU22" s="9"/>
-      <c r="AV22" s="9"/>
-      <c r="AW22" s="9"/>
-      <c r="AX22" s="9"/>
-      <c r="AY22" s="9"/>
-      <c r="AZ22" s="9"/>
-      <c r="BA22" s="9"/>
-      <c r="BB22" s="9"/>
-      <c r="BC22" s="9"/>
-      <c r="BD22" s="9"/>
-      <c r="BE22" s="9"/>
-      <c r="BF22" s="9"/>
-      <c r="BG22" s="10"/>
-      <c r="BI22" s="7"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+      <c r="AG22" s="22"/>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="22"/>
+      <c r="AK22" s="22"/>
+      <c r="AL22" s="22"/>
+      <c r="AM22" s="22"/>
+      <c r="AN22" s="22"/>
+      <c r="AO22" s="22"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="22"/>
+      <c r="AR22" s="22"/>
+      <c r="AS22" s="22"/>
+      <c r="AT22" s="22"/>
+      <c r="AU22" s="22"/>
+      <c r="AV22" s="22"/>
+      <c r="AW22" s="22"/>
+      <c r="AX22" s="22"/>
+      <c r="AY22" s="22"/>
+      <c r="AZ22" s="22"/>
+      <c r="BA22" s="22"/>
+      <c r="BB22" s="22"/>
+      <c r="BC22" s="22"/>
+      <c r="BD22" s="22"/>
+      <c r="BE22" s="22"/>
+      <c r="BF22" s="22"/>
+      <c r="BG22" s="23"/>
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="8"/>
+      <c r="BJ22" s="4"/>
     </row>
     <row r="23">
       <c r="B23" s="4"/>
-      <c r="D23" s="33" t="inlineStr">
+      <c r="C23" s="4"/>
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>（印鑑は鮮明に押</t>
         </is>
       </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" s="7"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="34" t="inlineStr">
+      <c r="Q23" s="9"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="38" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
-      <c r="AC23" s="12"/>
-      <c r="AD23" s="12"/>
-      <c r="AE23" s="12"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
-      <c r="AJ23" s="12"/>
-      <c r="AK23" s="12"/>
-      <c r="AL23" s="12"/>
-      <c r="AM23" s="12"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="12"/>
-      <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="12"/>
-      <c r="AT23" s="12"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="12"/>
-      <c r="AX23" s="12"/>
-      <c r="AY23" s="12"/>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-      <c r="BC23" s="12"/>
-      <c r="BD23" s="12"/>
-      <c r="BE23" s="12"/>
-      <c r="BF23" s="12"/>
-      <c r="BG23" s="14"/>
-      <c r="BH23" s="14"/>
-      <c r="BI23" s="7"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="10"/>
+      <c r="AK23" s="10"/>
+      <c r="AL23" s="10"/>
+      <c r="AM23" s="10"/>
+      <c r="AN23" s="10"/>
+      <c r="AO23" s="10"/>
+      <c r="AP23" s="10"/>
+      <c r="AQ23" s="10"/>
+      <c r="AR23" s="10"/>
+      <c r="AS23" s="10"/>
+      <c r="AT23" s="10"/>
+      <c r="AU23" s="10"/>
+      <c r="AV23" s="10"/>
+      <c r="AW23" s="10"/>
+      <c r="AX23" s="10"/>
+      <c r="AY23" s="10"/>
+      <c r="AZ23" s="10"/>
+      <c r="BA23" s="10"/>
+      <c r="BB23" s="10"/>
+      <c r="BC23" s="10"/>
+      <c r="BD23" s="10"/>
+      <c r="BE23" s="10"/>
+      <c r="BF23" s="10"/>
+      <c r="BG23" s="18"/>
+      <c r="BH23" s="11"/>
+      <c r="BI23" s="8"/>
+      <c r="BJ23" s="4"/>
     </row>
     <row r="24">
       <c r="B24" s="4"/>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="C24" s="4"/>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>印してください。）</t>
         </is>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
-      <c r="R24" s="23" t="inlineStr">
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="28" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="BH24" s="36"/>
-      <c r="BI24" s="7"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="23"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22"/>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="22"/>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="22"/>
+      <c r="AK24" s="22"/>
+      <c r="AL24" s="22"/>
+      <c r="AM24" s="22"/>
+      <c r="AN24" s="22"/>
+      <c r="AO24" s="22"/>
+      <c r="AP24" s="22"/>
+      <c r="AQ24" s="22"/>
+      <c r="AR24" s="22"/>
+      <c r="AS24" s="22"/>
+      <c r="AT24" s="22"/>
+      <c r="AU24" s="22"/>
+      <c r="AV24" s="22"/>
+      <c r="AW24" s="22"/>
+      <c r="AX24" s="22"/>
+      <c r="AY24" s="22"/>
+      <c r="AZ24" s="22"/>
+      <c r="BA24" s="22"/>
+      <c r="BB24" s="22"/>
+      <c r="BC24" s="22"/>
+      <c r="BD24" s="22"/>
+      <c r="BE24" s="22"/>
+      <c r="BF24" s="22"/>
+      <c r="BG24" s="23"/>
+      <c r="BH24" s="11"/>
+      <c r="BI24" s="8"/>
+      <c r="BJ24" s="4"/>
     </row>
     <row r="25">
       <c r="B25" s="4"/>
+      <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1972,15 +2114,15 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="X25" s="1"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
@@ -2016,43 +2158,89 @@
       <c r="BE25" s="2"/>
       <c r="BF25" s="2"/>
       <c r="BG25" s="3"/>
-      <c r="BH25" s="37"/>
-      <c r="BI25" s="7"/>
+      <c r="BH25" s="7"/>
+      <c r="BI25" s="8"/>
+      <c r="BJ25" s="4"/>
     </row>
     <row r="26">
       <c r="B26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="AA26" s="17" t="inlineStr">
+      <c r="E26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="36" t="inlineStr">
         <is>
           <t>委</t>
         </is>
       </c>
-      <c r="AG26" s="17" t="inlineStr">
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="16" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="AM26" s="17" t="inlineStr">
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
+      <c r="AM26" s="16" t="inlineStr">
         <is>
           <t>状</t>
         </is>
       </c>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="2"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="2"/>
+      <c r="AV26" s="2"/>
+      <c r="AW26" s="2"/>
+      <c r="AX26" s="2"/>
+      <c r="AY26" s="2"/>
+      <c r="AZ26" s="2"/>
+      <c r="BA26" s="2"/>
+      <c r="BB26" s="2"/>
+      <c r="BC26" s="2"/>
+      <c r="BD26" s="2"/>
+      <c r="BE26" s="2"/>
+      <c r="BF26" s="2"/>
       <c r="BG26" s="7"/>
-      <c r="BH26" s="38"/>
-      <c r="BI26" s="7"/>
+      <c r="BH26" s="20"/>
+      <c r="BI26" s="8"/>
+      <c r="BJ26" s="4"/>
     </row>
     <row r="27">
       <c r="B27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="39" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
@@ -2063,391 +2251,469 @@
           <t>私は、（住所）</t>
         </is>
       </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="14"/>
-      <c r="BG27" s="7"/>
-      <c r="BH27" s="38"/>
-      <c r="BI27" s="7"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+      <c r="AL27" s="2"/>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="1"/>
+      <c r="BG27" s="20"/>
+      <c r="BH27" s="20"/>
+      <c r="BI27" s="8"/>
+      <c r="BJ27" s="4"/>
     </row>
     <row r="28">
       <c r="B28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="G28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
       </c>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="14"/>
-      <c r="BG28" s="7"/>
-      <c r="BH28" s="38"/>
-      <c r="BI28" s="7"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="1"/>
+      <c r="BG28" s="20"/>
+      <c r="BH28" s="20"/>
+      <c r="BI28" s="8"/>
+      <c r="BJ28" s="4"/>
     </row>
     <row r="29">
       <c r="B29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>を代理人と定め、印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="BG29" s="7"/>
-      <c r="BH29" s="38"/>
-      <c r="BI29" s="7"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="1"/>
+      <c r="BG29" s="20"/>
+      <c r="BH29" s="20"/>
+      <c r="BI29" s="8"/>
+      <c r="BJ29" s="4"/>
     </row>
     <row r="30">
       <c r="B30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。</t>
         </is>
       </c>
-      <c r="BG30" s="7"/>
-      <c r="BH30" s="38"/>
-      <c r="BI30" s="7"/>
+      <c r="BG30" s="20"/>
+      <c r="BH30" s="20"/>
+      <c r="BI30" s="8"/>
+      <c r="BJ30" s="4"/>
     </row>
     <row r="31">
       <c r="B31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="O31" s="17" t="inlineStr">
+      <c r="O31" s="19" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="S31" s="17" t="inlineStr">
+      <c r="S31" s="19" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="W31" s="17" t="inlineStr">
+      <c r="W31" s="19" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="BG31" s="7"/>
-      <c r="BH31" s="38"/>
-      <c r="BI31" s="7"/>
+      <c r="BG31" s="20"/>
+      <c r="BH31" s="20"/>
+      <c r="BI31" s="8"/>
+      <c r="BJ31" s="4"/>
     </row>
     <row r="32">
       <c r="B32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="H32" s="1"/>
+      <c r="I32" s="16" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="BG32" s="7"/>
-      <c r="BH32" s="38"/>
-      <c r="BI32" s="7"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="1"/>
+      <c r="BG32" s="20"/>
+      <c r="BH32" s="20"/>
+      <c r="BI32" s="8"/>
+      <c r="BJ32" s="4"/>
     </row>
     <row r="33">
       <c r="B33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="AR33" s="17" t="inlineStr">
+      <c r="AR33" s="36" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
+      <c r="AS33" s="2"/>
+      <c r="AT33" s="1"/>
       <c r="AW33" s="40" t="inlineStr">
         <is>
           <t>登記所に提</t>
         </is>
       </c>
-      <c r="BG33" s="7"/>
-      <c r="BH33" s="38"/>
-      <c r="BI33" s="7"/>
+      <c r="BG33" s="20"/>
+      <c r="BH33" s="20"/>
+      <c r="BI33" s="8"/>
+      <c r="BJ33" s="4"/>
     </row>
     <row r="34">
       <c r="B34" s="4"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="E34" s="1"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
       </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
+      <c r="AJ34" s="2"/>
+      <c r="AK34" s="2"/>
+      <c r="AL34" s="2"/>
+      <c r="AM34" s="2"/>
+      <c r="AN34" s="2"/>
+      <c r="AO34" s="2"/>
+      <c r="AP34" s="2"/>
+      <c r="AQ34" s="2"/>
+      <c r="AR34" s="2"/>
+      <c r="AS34" s="2"/>
+      <c r="AT34" s="2"/>
+      <c r="AU34" s="2"/>
+      <c r="AV34" s="2"/>
+      <c r="AW34" s="2"/>
+      <c r="AX34" s="2"/>
+      <c r="AY34" s="2"/>
+      <c r="AZ34" s="2"/>
+      <c r="BA34" s="2"/>
+      <c r="BB34" s="2"/>
+      <c r="BC34" s="2"/>
+      <c r="BD34" s="2"/>
+      <c r="BE34" s="2"/>
+      <c r="BF34" s="2"/>
       <c r="BG34" s="7"/>
-      <c r="BH34" s="38"/>
-      <c r="BI34" s="7"/>
+      <c r="BH34" s="20"/>
+      <c r="BI34" s="8"/>
+      <c r="BJ34" s="4"/>
     </row>
     <row r="35">
       <c r="B35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="40" t="inlineStr">
         <is>
           <t>（注１）の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み登</t>
         </is>
       </c>
-      <c r="BG35" s="7"/>
-      <c r="BH35" s="38"/>
-      <c r="BI35" s="7"/>
+      <c r="BG35" s="8"/>
+      <c r="BH35" s="20"/>
+      <c r="BI35" s="8"/>
+      <c r="BJ35" s="4"/>
     </row>
     <row r="36">
       <c r="B36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
       <c r="I36" s="40" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
         </is>
       </c>
-      <c r="BG36" s="7"/>
-      <c r="BH36" s="38"/>
-      <c r="BI36" s="7"/>
+      <c r="BG36" s="8"/>
+      <c r="BH36" s="20"/>
+      <c r="BI36" s="8"/>
+      <c r="BJ36" s="4"/>
     </row>
     <row r="37">
       <c r="B37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="40" t="inlineStr">
         <is>
           <t>（注２）は、□にレ印をつけてください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
-      <c r="BG37" s="7"/>
-      <c r="BH37" s="38"/>
-      <c r="BI37" s="7"/>
+      <c r="BG37" s="8"/>
+      <c r="BH37" s="20"/>
+      <c r="BI37" s="8"/>
+      <c r="BJ37" s="4"/>
     </row>
     <row r="38">
       <c r="B38" s="4"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
       <c r="I38" s="40" t="inlineStr">
         <is>
           <t>事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。</t>
         </is>
       </c>
-      <c r="BG38" s="7"/>
-      <c r="BH38" s="38"/>
-      <c r="BI38" s="7"/>
+      <c r="BG38" s="8"/>
+      <c r="BH38" s="20"/>
+      <c r="BI38" s="8"/>
+      <c r="BJ38" s="4"/>
     </row>
     <row r="39">
       <c r="B39" s="4"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
       <c r="I39" s="40" t="inlineStr">
         <is>
           <t>村長の証明した印鑑証明書を添付してください。この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
         </is>
       </c>
-      <c r="BG39" s="7"/>
-      <c r="BH39" s="38"/>
-      <c r="BI39" s="7"/>
+      <c r="BG39" s="8"/>
+      <c r="BH39" s="20"/>
+      <c r="BI39" s="8"/>
+      <c r="BJ39" s="4"/>
     </row>
     <row r="40">
       <c r="B40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="40" t="inlineStr">
         <is>
           <t>（注３）印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
       </c>
-      <c r="AC40" s="36"/>
+      <c r="AC40" s="11"/>
       <c r="AD40" s="39" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
       </c>
-      <c r="AE40" s="12"/>
-      <c r="AF40" s="12"/>
-      <c r="AG40" s="12"/>
-      <c r="AH40" s="12"/>
-      <c r="AI40" s="12"/>
-      <c r="AJ40" s="12"/>
-      <c r="AK40" s="14"/>
-      <c r="AL40" s="19"/>
-      <c r="AM40" s="14"/>
+      <c r="AE40" s="10"/>
+      <c r="AF40" s="10"/>
+      <c r="AG40" s="10"/>
+      <c r="AH40" s="10"/>
+      <c r="AI40" s="10"/>
+      <c r="AJ40" s="10"/>
+      <c r="AK40" s="18"/>
+      <c r="AL40" s="9"/>
+      <c r="AM40" s="11"/>
       <c r="AN40" s="39" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
       </c>
-      <c r="AO40" s="12"/>
-      <c r="AP40" s="12"/>
-      <c r="AQ40" s="12"/>
-      <c r="AR40" s="14"/>
+      <c r="AO40" s="10"/>
+      <c r="AP40" s="10"/>
+      <c r="AQ40" s="10"/>
+      <c r="AR40" s="11"/>
       <c r="AS40" s="39" t="inlineStr">
         <is>
           <t>調 査</t>
         </is>
       </c>
-      <c r="AT40" s="12"/>
-      <c r="AU40" s="12"/>
-      <c r="AV40" s="12"/>
-      <c r="AW40" s="14"/>
+      <c r="AT40" s="10"/>
+      <c r="AU40" s="10"/>
+      <c r="AV40" s="10"/>
+      <c r="AW40" s="11"/>
       <c r="AX40" s="39" t="inlineStr">
         <is>
           <t>入 力</t>
         </is>
       </c>
-      <c r="AY40" s="12"/>
-      <c r="AZ40" s="12"/>
-      <c r="BA40" s="12"/>
-      <c r="BB40" s="14"/>
+      <c r="AY40" s="10"/>
+      <c r="AZ40" s="10"/>
+      <c r="BA40" s="10"/>
+      <c r="BB40" s="18"/>
       <c r="BC40" s="39" t="inlineStr">
         <is>
           <t>校 合</t>
         </is>
       </c>
-      <c r="BD40" s="12"/>
-      <c r="BE40" s="12"/>
-      <c r="BF40" s="12"/>
-      <c r="BG40" s="14"/>
-      <c r="BH40" s="36"/>
-      <c r="BI40" s="7"/>
+      <c r="BD40" s="9"/>
+      <c r="BE40" s="10"/>
+      <c r="BF40" s="10"/>
+      <c r="BG40" s="18"/>
+      <c r="BH40" s="11"/>
+      <c r="BI40" s="8"/>
+      <c r="BJ40" s="4"/>
     </row>
     <row r="41">
       <c r="B41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="41" t="inlineStr">
+      <c r="I41" s="40" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合には、(注１)の押印及び(注２)の委</t>
         </is>
       </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-      <c r="AA41" s="9"/>
-      <c r="AB41" s="9"/>
-      <c r="AC41" s="19"/>
-      <c r="AD41" s="12"/>
-      <c r="AE41" s="12"/>
-      <c r="AF41" s="12"/>
-      <c r="AG41" s="12"/>
-      <c r="AH41" s="12"/>
-      <c r="AI41" s="12"/>
-      <c r="AJ41" s="12"/>
-      <c r="AK41" s="12"/>
-      <c r="AL41" s="12"/>
-      <c r="AM41" s="14"/>
-      <c r="AN41" s="19"/>
-      <c r="AO41" s="12"/>
-      <c r="AP41" s="12"/>
-      <c r="AQ41" s="12"/>
-      <c r="AR41" s="14"/>
-      <c r="AS41" s="19"/>
-      <c r="AT41" s="12"/>
-      <c r="AU41" s="12"/>
-      <c r="AV41" s="12"/>
-      <c r="AW41" s="14"/>
-      <c r="AX41" s="19"/>
-      <c r="AY41" s="12"/>
-      <c r="AZ41" s="12"/>
-      <c r="BA41" s="12"/>
-      <c r="BB41" s="14"/>
-      <c r="BC41" s="19"/>
-      <c r="BD41" s="12"/>
-      <c r="BE41" s="12"/>
-      <c r="BF41" s="12"/>
-      <c r="BG41" s="14"/>
-      <c r="BH41" s="42"/>
-      <c r="BI41" s="7"/>
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="9"/>
+      <c r="AE41" s="10"/>
+      <c r="AF41" s="10"/>
+      <c r="AG41" s="10"/>
+      <c r="AH41" s="10"/>
+      <c r="AI41" s="10"/>
+      <c r="AJ41" s="10"/>
+      <c r="AK41" s="10"/>
+      <c r="AL41" s="9"/>
+      <c r="AM41" s="11"/>
+      <c r="AN41" s="9"/>
+      <c r="AO41" s="10"/>
+      <c r="AP41" s="10"/>
+      <c r="AQ41" s="10"/>
+      <c r="AR41" s="11"/>
+      <c r="AS41" s="9"/>
+      <c r="AT41" s="10"/>
+      <c r="AU41" s="10"/>
+      <c r="AV41" s="10"/>
+      <c r="AW41" s="11"/>
+      <c r="AX41" s="9"/>
+      <c r="AY41" s="10"/>
+      <c r="AZ41" s="10"/>
+      <c r="BA41" s="10"/>
+      <c r="BB41" s="18"/>
+      <c r="BC41" s="9"/>
+      <c r="BD41" s="9"/>
+      <c r="BE41" s="10"/>
+      <c r="BF41" s="10"/>
+      <c r="BG41" s="18"/>
+      <c r="BH41" s="11"/>
+      <c r="BI41" s="8"/>
+      <c r="BJ41" s="4"/>
     </row>
     <row r="42">
-      <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
       <c r="I42" s="41" t="inlineStr">
         <is>
           <t>任状は不要です。</t>
         </is>
       </c>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="9"/>
-      <c r="AE42" s="9"/>
-      <c r="AF42" s="9"/>
-      <c r="AG42" s="9"/>
-      <c r="AH42" s="9"/>
-      <c r="AI42" s="9"/>
-      <c r="AJ42" s="9"/>
-      <c r="AK42" s="9"/>
-      <c r="AL42" s="9"/>
-      <c r="AM42" s="10"/>
-      <c r="AN42" s="8"/>
-      <c r="AO42" s="9"/>
-      <c r="AP42" s="9"/>
-      <c r="AQ42" s="9"/>
-      <c r="AR42" s="10"/>
-      <c r="AS42" s="8"/>
-      <c r="AT42" s="9"/>
-      <c r="AU42" s="9"/>
-      <c r="AV42" s="9"/>
-      <c r="AW42" s="10"/>
-      <c r="AX42" s="8"/>
-      <c r="AY42" s="9"/>
-      <c r="AZ42" s="9"/>
-      <c r="BA42" s="9"/>
-      <c r="BB42" s="10"/>
-      <c r="BC42" s="8"/>
-      <c r="BD42" s="9"/>
-      <c r="BE42" s="9"/>
-      <c r="BF42" s="9"/>
-      <c r="BG42" s="10"/>
-      <c r="BH42" s="42"/>
-      <c r="BI42" s="10"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="22"/>
+      <c r="Y42" s="22"/>
+      <c r="Z42" s="22"/>
+      <c r="AA42" s="22"/>
+      <c r="AB42" s="22"/>
+      <c r="AC42" s="27"/>
+      <c r="AD42" s="22"/>
+      <c r="AE42" s="22"/>
+      <c r="AF42" s="22"/>
+      <c r="AG42" s="22"/>
+      <c r="AH42" s="22"/>
+      <c r="AI42" s="22"/>
+      <c r="AJ42" s="22"/>
+      <c r="AK42" s="22"/>
+      <c r="AL42" s="22"/>
+      <c r="AM42" s="30"/>
+      <c r="AN42" s="27"/>
+      <c r="AO42" s="22"/>
+      <c r="AP42" s="22"/>
+      <c r="AQ42" s="22"/>
+      <c r="AR42" s="23"/>
+      <c r="AS42" s="27"/>
+      <c r="AT42" s="22"/>
+      <c r="AU42" s="22"/>
+      <c r="AV42" s="22"/>
+      <c r="AW42" s="23"/>
+      <c r="AX42" s="27"/>
+      <c r="AY42" s="22"/>
+      <c r="AZ42" s="22"/>
+      <c r="BA42" s="22"/>
+      <c r="BB42" s="23"/>
+      <c r="BC42" s="27"/>
+      <c r="BD42" s="22"/>
+      <c r="BE42" s="22"/>
+      <c r="BF42" s="22"/>
+      <c r="BG42" s="23"/>
+      <c r="BH42" s="30"/>
+      <c r="BI42" s="23"/>
+      <c r="BJ42" s="4"/>
     </row>
     <row r="43">
-      <c r="D43" s="43" t="inlineStr">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>
@@ -2508,6 +2774,7 @@
       <c r="BF43" s="2"/>
       <c r="BG43" s="2"/>
       <c r="BH43" s="2"/>
+      <c r="BI43" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.43" right="0.43" top="0.41" bottom="0.41" header="0.5" footer="0.5"/>

--- a/data/out/test1/001328648_Python版_1pt.xlsx
+++ b/data/out/test1/001328648_Python版_1pt.xlsx
@@ -28,31 +28,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="19.6"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="10.9"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="9.800000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="8.800000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="7"/>
     </font>
   </fonts>
@@ -172,29 +172,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,64 +202,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,62 +627,62 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:BB46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="1.74" defaultRowHeight="18.25" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="1.65" defaultRowHeight="18.25" customHeight="1"/>
   <cols>
-    <col width="1.74" customWidth="1" min="1" max="1"/>
-    <col width="1.74" customWidth="1" min="2" max="2"/>
-    <col width="1.74" customWidth="1" min="3" max="3"/>
-    <col width="1.74" customWidth="1" min="4" max="4"/>
-    <col width="1.74" customWidth="1" min="5" max="5"/>
-    <col width="1.74" customWidth="1" min="6" max="6"/>
-    <col width="1.74" customWidth="1" min="7" max="7"/>
-    <col width="1.74" customWidth="1" min="8" max="8"/>
-    <col width="1.74" customWidth="1" min="9" max="9"/>
-    <col width="1.74" customWidth="1" min="10" max="10"/>
-    <col width="1.74" customWidth="1" min="11" max="11"/>
-    <col width="1.74" customWidth="1" min="12" max="12"/>
-    <col width="1.74" customWidth="1" min="13" max="13"/>
-    <col width="1.74" customWidth="1" min="14" max="14"/>
-    <col width="1.74" customWidth="1" min="15" max="15"/>
-    <col width="1.74" customWidth="1" min="16" max="16"/>
-    <col width="1.74" customWidth="1" min="17" max="17"/>
-    <col width="1.74" customWidth="1" min="18" max="18"/>
-    <col width="1.74" customWidth="1" min="19" max="19"/>
-    <col width="1.74" customWidth="1" min="20" max="20"/>
-    <col width="1.74" customWidth="1" min="21" max="21"/>
-    <col width="1.74" customWidth="1" min="22" max="22"/>
-    <col width="1.74" customWidth="1" min="23" max="23"/>
-    <col width="1.74" customWidth="1" min="24" max="24"/>
-    <col width="1.74" customWidth="1" min="25" max="25"/>
-    <col width="1.74" customWidth="1" min="26" max="26"/>
-    <col width="1.74" customWidth="1" min="27" max="27"/>
-    <col width="1.74" customWidth="1" min="28" max="28"/>
-    <col width="1.74" customWidth="1" min="29" max="29"/>
-    <col width="1.74" customWidth="1" min="30" max="30"/>
-    <col width="1.74" customWidth="1" min="31" max="31"/>
-    <col width="1.74" customWidth="1" min="32" max="32"/>
-    <col width="1.74" customWidth="1" min="33" max="33"/>
-    <col width="1.74" customWidth="1" min="34" max="34"/>
-    <col width="1.74" customWidth="1" min="35" max="35"/>
-    <col width="1.74" customWidth="1" min="36" max="36"/>
-    <col width="1.74" customWidth="1" min="37" max="37"/>
-    <col width="1.74" customWidth="1" min="38" max="38"/>
-    <col width="1.74" customWidth="1" min="39" max="39"/>
-    <col width="1.74" customWidth="1" min="40" max="40"/>
-    <col width="1.74" customWidth="1" min="41" max="41"/>
-    <col width="1.74" customWidth="1" min="42" max="42"/>
-    <col width="1.74" customWidth="1" min="43" max="43"/>
-    <col width="1.74" customWidth="1" min="44" max="44"/>
-    <col width="1.74" customWidth="1" min="45" max="45"/>
-    <col width="1.74" customWidth="1" min="46" max="46"/>
-    <col width="1.74" customWidth="1" min="47" max="47"/>
-    <col width="1.74" customWidth="1" min="48" max="48"/>
-    <col width="1.74" customWidth="1" min="49" max="49"/>
-    <col width="1.74" customWidth="1" min="50" max="50"/>
-    <col width="1.74" customWidth="1" min="51" max="51"/>
-    <col width="1.74" customWidth="1" min="52" max="52"/>
-    <col width="1.74" customWidth="1" min="53" max="53"/>
-    <col width="1.74" customWidth="1" min="54" max="54"/>
+    <col width="1.65" customWidth="1" min="1" max="1"/>
+    <col width="1.65" customWidth="1" min="2" max="2"/>
+    <col width="1.65" customWidth="1" min="3" max="3"/>
+    <col width="1.65" customWidth="1" min="4" max="4"/>
+    <col width="1.65" customWidth="1" min="5" max="5"/>
+    <col width="1.65" customWidth="1" min="6" max="6"/>
+    <col width="1.65" customWidth="1" min="7" max="7"/>
+    <col width="1.65" customWidth="1" min="8" max="8"/>
+    <col width="1.65" customWidth="1" min="9" max="9"/>
+    <col width="1.65" customWidth="1" min="10" max="10"/>
+    <col width="1.65" customWidth="1" min="11" max="11"/>
+    <col width="1.65" customWidth="1" min="12" max="12"/>
+    <col width="1.65" customWidth="1" min="13" max="13"/>
+    <col width="1.65" customWidth="1" min="14" max="14"/>
+    <col width="1.65" customWidth="1" min="15" max="15"/>
+    <col width="1.65" customWidth="1" min="16" max="16"/>
+    <col width="1.65" customWidth="1" min="17" max="17"/>
+    <col width="1.65" customWidth="1" min="18" max="18"/>
+    <col width="1.65" customWidth="1" min="19" max="19"/>
+    <col width="1.65" customWidth="1" min="20" max="20"/>
+    <col width="1.65" customWidth="1" min="21" max="21"/>
+    <col width="1.65" customWidth="1" min="22" max="22"/>
+    <col width="1.65" customWidth="1" min="23" max="23"/>
+    <col width="1.65" customWidth="1" min="24" max="24"/>
+    <col width="1.65" customWidth="1" min="25" max="25"/>
+    <col width="1.65" customWidth="1" min="26" max="26"/>
+    <col width="1.65" customWidth="1" min="27" max="27"/>
+    <col width="1.65" customWidth="1" min="28" max="28"/>
+    <col width="1.65" customWidth="1" min="29" max="29"/>
+    <col width="1.65" customWidth="1" min="30" max="30"/>
+    <col width="1.65" customWidth="1" min="31" max="31"/>
+    <col width="1.65" customWidth="1" min="32" max="32"/>
+    <col width="1.65" customWidth="1" min="33" max="33"/>
+    <col width="1.65" customWidth="1" min="34" max="34"/>
+    <col width="1.65" customWidth="1" min="35" max="35"/>
+    <col width="1.65" customWidth="1" min="36" max="36"/>
+    <col width="1.65" customWidth="1" min="37" max="37"/>
+    <col width="1.65" customWidth="1" min="38" max="38"/>
+    <col width="1.65" customWidth="1" min="39" max="39"/>
+    <col width="1.65" customWidth="1" min="40" max="40"/>
+    <col width="1.65" customWidth="1" min="41" max="41"/>
+    <col width="1.65" customWidth="1" min="42" max="42"/>
+    <col width="1.65" customWidth="1" min="43" max="43"/>
+    <col width="1.65" customWidth="1" min="44" max="44"/>
+    <col width="1.65" customWidth="1" min="45" max="45"/>
+    <col width="1.65" customWidth="1" min="46" max="46"/>
+    <col width="1.65" customWidth="1" min="47" max="47"/>
+    <col width="1.65" customWidth="1" min="48" max="48"/>
+    <col width="1.65" customWidth="1" min="49" max="49"/>
+    <col width="1.65" customWidth="1" min="50" max="50"/>
+    <col width="1.65" customWidth="1" min="51" max="51"/>
+    <col width="1.65" customWidth="1" min="52" max="52"/>
+    <col width="1.65" customWidth="1" min="53" max="53"/>
+    <col width="1.65" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1871,7 +1871,16 @@
           <t>（印印し鑑てはくだ鮮さ明いに。押）</t>
         </is>
       </c>
-      <c r="N25" s="12"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="9"/>
       <c r="O25" s="1"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
@@ -1911,13 +1920,13 @@
       <c r="AY25" s="10"/>
       <c r="AZ25" s="2"/>
       <c r="BA25" s="1"/>
-      <c r="BB25" s="3"/>
+      <c r="BB25" s="9"/>
     </row>
     <row r="26">
       <c r="B26" s="3"/>
       <c r="C26" s="19"/>
       <c r="D26" s="13"/>
-      <c r="E26" s="17"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
@@ -1969,22 +1978,22 @@
       <c r="AX26" s="17"/>
       <c r="AY26" s="18"/>
       <c r="BA26" s="1"/>
-      <c r="BB26" s="3"/>
+      <c r="BB26" s="12"/>
     </row>
     <row r="27">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="1"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="19"/>
       <c r="O27" s="1"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
@@ -2024,12 +2033,17 @@
       <c r="AY27" s="10"/>
       <c r="AZ27" s="2"/>
       <c r="BA27" s="1"/>
-      <c r="BB27" s="3"/>
+      <c r="BB27" s="12"/>
     </row>
     <row r="28">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
       <c r="X28" s="6" t="inlineStr">
         <is>
           <t>委</t>
@@ -2056,12 +2070,13 @@
       <c r="AI28" s="1"/>
       <c r="AY28" s="30"/>
       <c r="BA28" s="3"/>
-      <c r="BB28" s="3"/>
+      <c r="BB28" s="12"/>
     </row>
     <row r="29">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
       <c r="G29" s="36" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
@@ -2081,12 +2096,13 @@
       <c r="O29" s="2"/>
       <c r="AY29" s="30"/>
       <c r="BA29" s="3"/>
-      <c r="BB29" s="3"/>
+      <c r="BB29" s="12"/>
     </row>
     <row r="30">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
       <c r="G30" s="1"/>
       <c r="H30" s="2"/>
       <c r="I30" s="36" t="inlineStr">
@@ -2106,12 +2122,13 @@
       <c r="O30" s="1"/>
       <c r="AY30" s="30"/>
       <c r="BA30" s="3"/>
-      <c r="BB30" s="3"/>
+      <c r="BB30" s="12"/>
     </row>
     <row r="31">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
           <t>を代理人と定め、印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
@@ -2126,12 +2143,13 @@
       <c r="O31" s="1"/>
       <c r="AY31" s="30"/>
       <c r="BA31" s="3"/>
-      <c r="BB31" s="3"/>
+      <c r="BB31" s="12"/>
     </row>
     <row r="32">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
           <t>の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。</t>
@@ -2139,12 +2157,13 @@
       </c>
       <c r="AY32" s="30"/>
       <c r="BA32" s="3"/>
-      <c r="BB32" s="3"/>
+      <c r="BB32" s="12"/>
     </row>
     <row r="33">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
       <c r="M33" s="11" t="inlineStr">
         <is>
           <t>年</t>
@@ -2162,12 +2181,13 @@
       </c>
       <c r="AY33" s="30"/>
       <c r="BA33" s="3"/>
-      <c r="BB33" s="3"/>
+      <c r="BB33" s="12"/>
     </row>
     <row r="34">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
       <c r="G34" s="1"/>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -2179,12 +2199,13 @@
       <c r="K34" s="1"/>
       <c r="AY34" s="30"/>
       <c r="BA34" s="3"/>
-      <c r="BB34" s="3"/>
+      <c r="BB34" s="12"/>
     </row>
     <row r="35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
       <c r="G35" s="1"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -2207,13 +2228,13 @@
       </c>
       <c r="AY35" s="30"/>
       <c r="BA35" s="3"/>
-      <c r="BB35" s="3"/>
+      <c r="BB35" s="12"/>
     </row>
     <row r="36">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="2"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
@@ -2266,7 +2287,7 @@
       <c r="AY36" s="10"/>
       <c r="AZ36" s="2"/>
       <c r="BA36" s="3"/>
-      <c r="BB36" s="3"/>
+      <c r="BB36" s="12"/>
     </row>
     <row r="37">
       <c r="B37" s="3"/>
@@ -2276,13 +2297,15 @@
           <t>（注１）登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
+      <c r="E37" s="3"/>
       <c r="AY37" s="30"/>
       <c r="BA37" s="3"/>
-      <c r="BB37" s="3"/>
+      <c r="BB37" s="12"/>
     </row>
     <row r="38">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
+      <c r="E38" s="3"/>
       <c r="H38" s="38" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
@@ -2290,11 +2313,12 @@
       </c>
       <c r="AY38" s="30"/>
       <c r="BA38" s="3"/>
-      <c r="BB38" s="3"/>
+      <c r="BB38" s="12"/>
     </row>
     <row r="39">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
+      <c r="E39" s="3"/>
       <c r="H39" s="38" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）は、□にレ印をつけてください。</t>
@@ -2302,7 +2326,7 @@
       </c>
       <c r="AY39" s="30"/>
       <c r="BA39" s="3"/>
-      <c r="BB39" s="3"/>
+      <c r="BB39" s="12"/>
     </row>
     <row r="40">
       <c r="B40" s="3"/>
@@ -2312,21 +2336,68 @@
           <t>（注２）代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
+      <c r="E40" s="3"/>
       <c r="AY40" s="30"/>
       <c r="BA40" s="3"/>
-      <c r="BB40" s="3"/>
+      <c r="BB40" s="12"/>
     </row>
     <row r="41">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="H41" s="38" t="inlineStr">
+      <c r="E41" s="13"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。</t>
         </is>
       </c>
-      <c r="AY41" s="30"/>
-      <c r="BA41" s="3"/>
-      <c r="BB41" s="3"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17"/>
+      <c r="AB41" s="17"/>
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
+      <c r="AF41" s="17"/>
+      <c r="AG41" s="17"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="17"/>
+      <c r="AJ41" s="17"/>
+      <c r="AK41" s="17"/>
+      <c r="AL41" s="17"/>
+      <c r="AM41" s="17"/>
+      <c r="AN41" s="17"/>
+      <c r="AO41" s="17"/>
+      <c r="AP41" s="17"/>
+      <c r="AQ41" s="17"/>
+      <c r="AR41" s="17"/>
+      <c r="AS41" s="17"/>
+      <c r="AT41" s="17"/>
+      <c r="AU41" s="17"/>
+      <c r="AV41" s="17"/>
+      <c r="AW41" s="17"/>
+      <c r="AX41" s="17"/>
+      <c r="AY41" s="18"/>
+      <c r="AZ41" s="17"/>
+      <c r="BA41" s="13"/>
+      <c r="BB41" s="25"/>
     </row>
     <row r="42">
       <c r="B42" s="3"/>
@@ -2381,7 +2452,7 @@
         </is>
       </c>
       <c r="Y43" s="21"/>
-      <c r="Z43" s="39" t="inlineStr">
+      <c r="Z43" s="40" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
@@ -2394,7 +2465,7 @@
       <c r="AF43" s="16"/>
       <c r="AG43" s="15"/>
       <c r="AH43" s="21"/>
-      <c r="AI43" s="39" t="inlineStr">
+      <c r="AI43" s="40" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
@@ -2438,7 +2509,7 @@
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
       <c r="G44" s="17"/>
-      <c r="H44" s="40" t="inlineStr">
+      <c r="H44" s="39" t="inlineStr">
         <is>
           <t>には、(注１)の押印及び(注２)の委任状は不要です。</t>
         </is>
